--- a/Synsam modell.xlsx
+++ b/Synsam modell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/augusthodt/Desktop/Aksjemodellering/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45294C3-3159-FD47-9E4F-534C23B66213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201F7789-2317-F348-9481-32AFE62E624C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25180" yWindow="500" windowWidth="26020" windowHeight="26740" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17220" activeTab="1" xr2:uid="{5AE0DF26-B7DD-1242-A60E-253C73A930AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="206">
   <si>
     <t>Kapitalstruktur</t>
   </si>
@@ -699,7 +699,28 @@
     <t>01.09.25: Synsam kjøper tilbake 100 000 aksjer</t>
   </si>
   <si>
-    <t>21.08.25: Synsam starter tilbaekkjøpsprgram for å justerer kapitalstrukturen sin</t>
+    <t>08.06.26: Synsam kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>21.08.25: Synsam starter tilbakekjøpsprgram for å justerer kapitalstrukturen sin</t>
+  </si>
+  <si>
+    <t>P/B</t>
+  </si>
+  <si>
+    <t>15.06.26: Synsam kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>22.06.26: Synsam kjøper tilbake 99 445 aksjer</t>
+  </si>
+  <si>
+    <t>29.06.26: Synsam kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>06.07.26: Synsam kjøper tilbake 125 000 aksjer</t>
+  </si>
+  <si>
+    <t>13.07.26: Synsam kjøper tilbake 130 000 aksjer</t>
   </si>
 </sst>
 </file>
@@ -920,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -944,7 +965,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1006,10 +1026,6 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2121,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D6FABC2-1253-924E-8CB2-F0C03750A097}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="10.83203125" style="2"/>
@@ -2168,31 +2184,31 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="N8" s="77" t="s">
+      <c r="N8" s="76" t="s">
         <v>162</v>
       </c>
-      <c r="O8" s="77"/>
-      <c r="P8" s="78"/>
-      <c r="Q8" s="78"/>
-      <c r="R8" s="78"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="77"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="77"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="N9" s="77" t="s">
+      <c r="N9" s="76" t="s">
         <v>163</v>
       </c>
-      <c r="O9" s="77" t="s">
+      <c r="O9" s="76" t="s">
         <v>164</v>
       </c>
-      <c r="P9" s="77" t="s">
+      <c r="P9" s="76" t="s">
         <v>165</v>
       </c>
-      <c r="Q9" s="77" t="s">
+      <c r="Q9" s="76" t="s">
         <v>166</v>
       </c>
-      <c r="R9" s="77" t="s">
+      <c r="R9" s="76" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2224,174 +2240,204 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>129</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>130</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>198</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2503,7 +2549,7 @@
       <c r="S3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="T3" s="39" t="s">
+      <c r="T3" s="38" t="s">
         <v>112</v>
       </c>
       <c r="U3" s="4" t="s">
@@ -2534,7 +2580,7 @@
       <c r="AF3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="AG3" s="39" t="s">
+      <c r="AG3" s="38" t="s">
         <v>17</v>
       </c>
       <c r="AH3" s="4" t="s">
@@ -2570,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <v>54.4</v>
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>49</v>
@@ -2623,7 +2669,7 @@
       <c r="S4" s="16">
         <v>1834</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="27">
         <v>1801</v>
       </c>
       <c r="AA4" s="16">
@@ -2644,7 +2690,7 @@
       <c r="AF4" s="16">
         <v>7200</v>
       </c>
-      <c r="AG4" s="28">
+      <c r="AG4" s="27">
         <f>AF4*1.06</f>
         <v>7632</v>
       </c>
@@ -2811,7 +2857,7 @@
       </c>
       <c r="B6" s="8">
         <f>B4*B5</f>
-        <v>7769.3068159999993</v>
+        <v>7854.9976999999999</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
@@ -3199,7 +3245,7 @@
       </c>
       <c r="B9" s="9">
         <f>B6-B7+B8</f>
-        <v>9761.3068160000003</v>
+        <v>9846.9976999999999</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>54</v>
@@ -3268,11 +3314,11 @@
         <f>SUM(S6:S8)</f>
         <v>426</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="27">
         <f>SUM(T6:T8)</f>
         <v>400</v>
       </c>
-      <c r="Y9" s="34"/>
+      <c r="Y9" s="33"/>
       <c r="AA9" s="16">
         <f t="shared" ref="AA9:AE9" si="10">SUM(AA6:AA8)</f>
         <v>934</v>
@@ -3297,7 +3343,7 @@
         <f>SUM(AF6:AF8)</f>
         <v>1688</v>
       </c>
-      <c r="AG9" s="28">
+      <c r="AG9" s="27">
         <f t="shared" ref="AG9:AP9" si="11">SUM(AG6:AG8)</f>
         <v>1871.7599999999998</v>
       </c>
@@ -3415,43 +3461,43 @@
         <v>-702</v>
       </c>
       <c r="AG10" s="18">
-        <v>-800</v>
+        <v>-820</v>
       </c>
       <c r="AH10" s="15">
         <f>AG10*1.06</f>
-        <v>-848</v>
+        <v>-869.2</v>
       </c>
       <c r="AI10" s="15">
         <f t="shared" ref="AI10:AP10" si="12">AH10*1.01</f>
-        <v>-856.48</v>
+        <v>-877.89200000000005</v>
       </c>
       <c r="AJ10" s="15">
         <f t="shared" si="12"/>
-        <v>-865.04480000000001</v>
+        <v>-886.67092000000002</v>
       </c>
       <c r="AK10" s="15">
         <f t="shared" si="12"/>
-        <v>-873.69524799999999</v>
+        <v>-895.53762920000008</v>
       </c>
       <c r="AL10" s="15">
         <f t="shared" si="12"/>
-        <v>-882.43220048000001</v>
+        <v>-904.49300549200007</v>
       </c>
       <c r="AM10" s="15">
         <f t="shared" si="12"/>
-        <v>-891.25652248480003</v>
+        <v>-913.53793554692004</v>
       </c>
       <c r="AN10" s="15">
         <f t="shared" si="12"/>
-        <v>-900.16908770964801</v>
+        <v>-922.67331490238928</v>
       </c>
       <c r="AO10" s="15">
         <f t="shared" si="12"/>
-        <v>-909.17077858674452</v>
+        <v>-931.90004805141314</v>
       </c>
       <c r="AP10" s="15">
         <f t="shared" si="12"/>
-        <v>-918.26248637261199</v>
+        <v>-941.21904853192723</v>
       </c>
     </row>
     <row r="11" spans="1:42" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -3524,11 +3570,11 @@
         <f>SUM(S9:S10)</f>
         <v>246</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="27">
         <f>SUM(T9:T10)</f>
         <v>218</v>
       </c>
-      <c r="Y11" s="33"/>
+      <c r="Y11" s="32"/>
       <c r="AA11" s="16">
         <f t="shared" ref="AA11:AE11" si="15">SUM(AA9:AA10)</f>
         <v>489</v>
@@ -3553,45 +3599,45 @@
         <f>SUM(AF9:AF10)</f>
         <v>986</v>
       </c>
-      <c r="AG11" s="28">
+      <c r="AG11" s="27">
         <f t="shared" ref="AG11:AP11" si="16">SUM(AG9:AG10)</f>
-        <v>1071.7599999999998</v>
+        <v>1051.7599999999998</v>
       </c>
       <c r="AH11" s="16">
         <f t="shared" si="16"/>
-        <v>1155.7083999999995</v>
+        <v>1134.5083999999995</v>
       </c>
       <c r="AI11" s="16">
         <f t="shared" si="16"/>
-        <v>1288.1740580000005</v>
+        <v>1266.7620580000005</v>
       </c>
       <c r="AJ11" s="16">
         <f t="shared" si="16"/>
-        <v>1408.2885014800017</v>
+        <v>1386.6623814800018</v>
       </c>
       <c r="AK11" s="16">
         <f t="shared" si="16"/>
-        <v>1536.0380515688021</v>
+        <v>1514.195670368802</v>
       </c>
       <c r="AL11" s="16">
         <f t="shared" si="16"/>
-        <v>1671.8850970629287</v>
+        <v>1649.8242920509288</v>
       </c>
       <c r="AM11" s="16">
         <f t="shared" si="16"/>
-        <v>1816.3198129107054</v>
+        <v>1794.0383998485854</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="16"/>
-        <v>1969.8618278095882</v>
+        <v>1947.3576006168469</v>
       </c>
       <c r="AO11" s="16">
         <f t="shared" si="16"/>
-        <v>2133.0619918636448</v>
+        <v>2110.3327223989763</v>
       </c>
       <c r="AP11" s="16">
         <f t="shared" si="16"/>
-        <v>2306.504250304803</v>
+        <v>2283.5476881454879</v>
       </c>
     </row>
     <row r="12" spans="1:42" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -3785,10 +3831,11 @@
         <f>SUM(S11:S12)</f>
         <v>214</v>
       </c>
-      <c r="T13" s="28">
+      <c r="T13" s="27">
         <f>SUM(T11:T12)</f>
         <v>186</v>
       </c>
+      <c r="V13" s="32"/>
       <c r="AA13" s="16">
         <f t="shared" ref="AA13:AE13" si="20">SUM(AA11:AA12)</f>
         <v>402</v>
@@ -3813,50 +3860,50 @@
         <f>SUM(AF11:AF12)</f>
         <v>862</v>
       </c>
-      <c r="AG13" s="28">
+      <c r="AG13" s="27">
         <f t="shared" ref="AG13:AP13" si="21">SUM(AG11:AG12)</f>
-        <v>943.75999999999976</v>
+        <v>923.75999999999976</v>
       </c>
       <c r="AH13" s="16">
         <f t="shared" si="21"/>
-        <v>1022.5883999999995</v>
+        <v>1001.3883999999995</v>
       </c>
       <c r="AI13" s="16">
         <f t="shared" si="21"/>
-        <v>1153.7228580000005</v>
+        <v>1132.3108580000005</v>
       </c>
       <c r="AJ13" s="16">
         <f t="shared" si="21"/>
-        <v>1272.4927894800016</v>
+        <v>1250.8666694800017</v>
       </c>
       <c r="AK13" s="16">
         <f t="shared" si="21"/>
-        <v>1398.8843824488022</v>
+        <v>1377.0420012488021</v>
       </c>
       <c r="AL13" s="16">
         <f t="shared" si="21"/>
-        <v>1533.3598912517286</v>
+        <v>1511.2990862397287</v>
       </c>
       <c r="AM13" s="16">
         <f t="shared" si="21"/>
-        <v>1676.4093550413934</v>
+        <v>1654.1279419792734</v>
       </c>
       <c r="AN13" s="16">
         <f t="shared" si="21"/>
-        <v>1828.5522653615831</v>
+        <v>1806.0480381688417</v>
       </c>
       <c r="AO13" s="16">
         <f t="shared" si="21"/>
-        <v>1990.3393337911596</v>
+        <v>1967.6100643264911</v>
       </c>
       <c r="AP13" s="16">
         <f t="shared" si="21"/>
-        <v>2162.3543656515931</v>
+        <v>2139.3978034922779</v>
       </c>
     </row>
     <row r="14" spans="1:42" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
-      <c r="B14" s="28"/>
+      <c r="B14" s="27"/>
       <c r="C14" s="2" t="s">
         <v>59</v>
       </c>
@@ -3971,8 +4018,13 @@
       </c>
     </row>
     <row r="15" spans="1:42" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="21"/>
+      <c r="A15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" s="11">
+        <f>B6/+T54</f>
+        <v>3.0141971220260935</v>
+      </c>
       <c r="C15" s="2" t="s">
         <v>60</v>
       </c>
@@ -4088,7 +4140,7 @@
     </row>
     <row r="16" spans="1:42" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="2" t="s">
         <v>61</v>
       </c>
@@ -4186,43 +4238,43 @@
       </c>
       <c r="AG16" s="18">
         <f t="shared" ref="AG16:AP16" si="27">SUM(AG13:AG15)</f>
-        <v>666.31999999999982</v>
+        <v>646.31999999999982</v>
       </c>
       <c r="AH16" s="15">
         <f t="shared" si="27"/>
-        <v>739.59959999999955</v>
+        <v>718.39959999999951</v>
       </c>
       <c r="AI16" s="15">
         <f t="shared" si="27"/>
-        <v>865.07428200000049</v>
+        <v>843.66228200000046</v>
       </c>
       <c r="AJ16" s="15">
         <f t="shared" si="27"/>
-        <v>978.07124196000154</v>
+        <v>956.44512196000164</v>
       </c>
       <c r="AK16" s="15">
         <f t="shared" si="27"/>
-        <v>1098.5744039784022</v>
+        <v>1076.7320227784021</v>
       </c>
       <c r="AL16" s="15">
         <f t="shared" si="27"/>
-        <v>1227.0437132119205</v>
+        <v>1204.9829081999205</v>
       </c>
       <c r="AM16" s="15">
         <f t="shared" si="27"/>
-        <v>1363.966853440789</v>
+        <v>1341.685440378669</v>
       </c>
       <c r="AN16" s="15">
         <f t="shared" si="27"/>
-        <v>1509.8609137289668</v>
+        <v>1487.3566865362254</v>
       </c>
       <c r="AO16" s="15">
         <f t="shared" si="27"/>
-        <v>1665.274155125891</v>
+        <v>1642.5448856612225</v>
       </c>
       <c r="AP16" s="15">
         <f t="shared" si="27"/>
-        <v>1830.7878834130188</v>
+        <v>1807.8313212537037</v>
       </c>
     </row>
     <row r="17" spans="1:206" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -4301,48 +4353,48 @@
       </c>
       <c r="AG17" s="18">
         <f>AG16*-0.2</f>
-        <v>-133.26399999999998</v>
+        <v>-129.26399999999998</v>
       </c>
       <c r="AH17" s="15">
         <f t="shared" ref="AH17:AP17" si="28">AH16*-0.2</f>
-        <v>-147.91991999999991</v>
+        <v>-143.6799199999999</v>
       </c>
       <c r="AI17" s="15">
         <f t="shared" si="28"/>
-        <v>-173.0148564000001</v>
+        <v>-168.7324564000001</v>
       </c>
       <c r="AJ17" s="15">
         <f t="shared" si="28"/>
-        <v>-195.61424839200032</v>
+        <v>-191.28902439200033</v>
       </c>
       <c r="AK17" s="15">
         <f t="shared" si="28"/>
-        <v>-219.71488079568044</v>
+        <v>-215.34640455568044</v>
       </c>
       <c r="AL17" s="15">
         <f t="shared" si="28"/>
-        <v>-245.40874264238411</v>
+        <v>-240.99658163998413</v>
       </c>
       <c r="AM17" s="15">
         <f t="shared" si="28"/>
-        <v>-272.79337068815784</v>
+        <v>-268.33708807573379</v>
       </c>
       <c r="AN17" s="15">
         <f t="shared" si="28"/>
-        <v>-301.97218274579336</v>
+        <v>-297.47133730724511</v>
       </c>
       <c r="AO17" s="15">
         <f t="shared" si="28"/>
-        <v>-333.0548310251782</v>
+        <v>-328.50897713224452</v>
       </c>
       <c r="AP17" s="15">
         <f t="shared" si="28"/>
-        <v>-366.1575766826038</v>
+        <v>-361.56626425074074</v>
       </c>
     </row>
     <row r="18" spans="1:206" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="22"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="1" t="s">
         <v>63</v>
       </c>
@@ -4410,7 +4462,7 @@
         <f>SUM(S16:S17)</f>
         <v>122</v>
       </c>
-      <c r="T18" s="28">
+      <c r="T18" s="27">
         <f>SUM(T16:T17)</f>
         <v>130</v>
       </c>
@@ -4438,782 +4490,782 @@
         <f>SUM(AF16:AF17)</f>
         <v>454</v>
       </c>
-      <c r="AG18" s="28">
+      <c r="AG18" s="27">
         <f t="shared" ref="AG18:AP18" si="32">SUM(AG16:AG17)</f>
-        <v>533.05599999999981</v>
+        <v>517.05599999999981</v>
       </c>
       <c r="AH18" s="16">
         <f t="shared" si="32"/>
-        <v>591.67967999999962</v>
+        <v>574.71967999999958</v>
       </c>
       <c r="AI18" s="16">
         <f t="shared" si="32"/>
-        <v>692.0594256000004</v>
+        <v>674.92982560000041</v>
       </c>
       <c r="AJ18" s="16">
         <f t="shared" si="32"/>
-        <v>782.45699356800128</v>
+        <v>765.15609756800131</v>
       </c>
       <c r="AK18" s="16">
         <f t="shared" si="32"/>
-        <v>878.85952318272177</v>
+        <v>861.38561822272163</v>
       </c>
       <c r="AL18" s="16">
         <f t="shared" si="32"/>
-        <v>981.63497056953634</v>
+        <v>963.9863265599364</v>
       </c>
       <c r="AM18" s="16">
         <f t="shared" si="32"/>
-        <v>1091.1734827526311</v>
+        <v>1073.3483523029352</v>
       </c>
       <c r="AN18" s="16">
         <f t="shared" si="32"/>
-        <v>1207.8887309831734</v>
+        <v>1189.8853492289804</v>
       </c>
       <c r="AO18" s="16">
         <f t="shared" si="32"/>
-        <v>1332.2193241007128</v>
+        <v>1314.0359085289779</v>
       </c>
       <c r="AP18" s="16">
         <f t="shared" si="32"/>
-        <v>1464.630306730415</v>
+        <v>1446.265057002963</v>
       </c>
       <c r="AQ18" s="16">
         <f>AP18*(1+$AS$22)</f>
-        <v>1449.9840036631108</v>
+        <v>1431.8024064329334</v>
       </c>
       <c r="AR18" s="16">
         <f t="shared" ref="AR18:DC18" si="33">AQ18*(1+$AS$22)</f>
-        <v>1435.4841636264796</v>
+        <v>1417.484382368604</v>
       </c>
       <c r="AS18" s="16">
         <f t="shared" si="33"/>
-        <v>1421.1293219902147</v>
+        <v>1403.3095385449178</v>
       </c>
       <c r="AT18" s="16">
         <f t="shared" si="33"/>
-        <v>1406.9180287703125</v>
+        <v>1389.2764431594687</v>
       </c>
       <c r="AU18" s="16">
         <f t="shared" si="33"/>
-        <v>1392.8488484826094</v>
+        <v>1375.383678727874</v>
       </c>
       <c r="AV18" s="16">
         <f t="shared" si="33"/>
-        <v>1378.9203599977832</v>
+        <v>1361.6298419405953</v>
       </c>
       <c r="AW18" s="16">
         <f t="shared" si="33"/>
-        <v>1365.1311563978054</v>
+        <v>1348.0135435211894</v>
       </c>
       <c r="AX18" s="16">
         <f t="shared" si="33"/>
-        <v>1351.4798448338274</v>
+        <v>1334.5334080859775</v>
       </c>
       <c r="AY18" s="16">
         <f t="shared" si="33"/>
-        <v>1337.9650463854891</v>
+        <v>1321.1880740051176</v>
       </c>
       <c r="AZ18" s="16">
         <f t="shared" si="33"/>
-        <v>1324.5853959216342</v>
+        <v>1307.9761932650665</v>
       </c>
       <c r="BA18" s="16">
         <f t="shared" si="33"/>
-        <v>1311.3395419624178</v>
+        <v>1294.8964313324159</v>
       </c>
       <c r="BB18" s="16">
         <f t="shared" si="33"/>
-        <v>1298.2261465427937</v>
+        <v>1281.9474670190916</v>
       </c>
       <c r="BC18" s="16">
         <f t="shared" si="33"/>
-        <v>1285.2438850773658</v>
+        <v>1269.1279923489008</v>
       </c>
       <c r="BD18" s="16">
         <f t="shared" si="33"/>
-        <v>1272.3914462265921</v>
+        <v>1256.4367124254118</v>
       </c>
       <c r="BE18" s="16">
         <f t="shared" si="33"/>
-        <v>1259.6675317643262</v>
+        <v>1243.8723453011576</v>
       </c>
       <c r="BF18" s="16">
         <f t="shared" si="33"/>
-        <v>1247.0708564466829</v>
+        <v>1231.433621848146</v>
       </c>
       <c r="BG18" s="16">
         <f t="shared" si="33"/>
-        <v>1234.6001478822161</v>
+        <v>1219.1192856296645</v>
       </c>
       <c r="BH18" s="16">
         <f t="shared" si="33"/>
-        <v>1222.2541464033939</v>
+        <v>1206.9280927733678</v>
       </c>
       <c r="BI18" s="16">
         <f t="shared" si="33"/>
-        <v>1210.03160493936</v>
+        <v>1194.8588118456341</v>
       </c>
       <c r="BJ18" s="16">
         <f t="shared" si="33"/>
-        <v>1197.9312888899665</v>
+        <v>1182.9102237271777</v>
       </c>
       <c r="BK18" s="16">
         <f t="shared" si="33"/>
-        <v>1185.9519760010669</v>
+        <v>1171.0811214899059</v>
       </c>
       <c r="BL18" s="16">
         <f t="shared" si="33"/>
-        <v>1174.0924562410562</v>
+        <v>1159.3703102750069</v>
       </c>
       <c r="BM18" s="16">
         <f t="shared" si="33"/>
-        <v>1162.3515316786456</v>
+        <v>1147.7766071722567</v>
       </c>
       <c r="BN18" s="16">
         <f t="shared" si="33"/>
-        <v>1150.7280163618591</v>
+        <v>1136.2988411005342</v>
       </c>
       <c r="BO18" s="16">
         <f t="shared" si="33"/>
-        <v>1139.2207361982405</v>
+        <v>1124.9358526895289</v>
       </c>
       <c r="BP18" s="16">
         <f t="shared" si="33"/>
-        <v>1127.8285288362581</v>
+        <v>1113.6864941626336</v>
       </c>
       <c r="BQ18" s="16">
         <f t="shared" si="33"/>
-        <v>1116.5502435478954</v>
+        <v>1102.5496292210073</v>
       </c>
       <c r="BR18" s="16">
         <f t="shared" si="33"/>
-        <v>1105.3847411124166</v>
+        <v>1091.5241329287971</v>
       </c>
       <c r="BS18" s="16">
         <f t="shared" si="33"/>
-        <v>1094.3308937012923</v>
+        <v>1080.6088915995092</v>
       </c>
       <c r="BT18" s="16">
         <f t="shared" si="33"/>
-        <v>1083.3875847642794</v>
+        <v>1069.8028026835141</v>
       </c>
       <c r="BU18" s="16">
         <f t="shared" si="33"/>
-        <v>1072.5537089166367</v>
+        <v>1059.104774656679</v>
       </c>
       <c r="BV18" s="16">
         <f t="shared" si="33"/>
-        <v>1061.8281718274702</v>
+        <v>1048.5137269101122</v>
       </c>
       <c r="BW18" s="16">
         <f t="shared" si="33"/>
-        <v>1051.2098901091956</v>
+        <v>1038.028589641011</v>
       </c>
       <c r="BX18" s="16">
         <f t="shared" si="33"/>
-        <v>1040.6977912081036</v>
+        <v>1027.6483037446008</v>
       </c>
       <c r="BY18" s="16">
         <f t="shared" si="33"/>
-        <v>1030.2908132960226</v>
+        <v>1017.3718207071547</v>
       </c>
       <c r="BZ18" s="16">
         <f t="shared" si="33"/>
-        <v>1019.9879051630624</v>
+        <v>1007.1981025000831</v>
       </c>
       <c r="CA18" s="16">
         <f t="shared" si="33"/>
-        <v>1009.7880261114317</v>
+        <v>997.1261214750823</v>
       </c>
       <c r="CB18" s="16">
         <f t="shared" si="33"/>
-        <v>999.69014585031732</v>
+        <v>987.15486026033147</v>
       </c>
       <c r="CC18" s="16">
         <f t="shared" si="33"/>
-        <v>989.69324439181412</v>
+        <v>977.28331165772818</v>
       </c>
       <c r="CD18" s="16">
         <f t="shared" si="33"/>
-        <v>979.79631194789602</v>
+        <v>967.51047854115086</v>
       </c>
       <c r="CE18" s="16">
         <f t="shared" si="33"/>
-        <v>969.99834882841708</v>
+        <v>957.8353737557394</v>
       </c>
       <c r="CF18" s="16">
         <f t="shared" si="33"/>
-        <v>960.29836534013293</v>
+        <v>948.25702001818195</v>
       </c>
       <c r="CG18" s="16">
         <f t="shared" si="33"/>
-        <v>950.69538168673159</v>
+        <v>938.77444981800011</v>
       </c>
       <c r="CH18" s="16">
         <f t="shared" si="33"/>
-        <v>941.18842786986431</v>
+        <v>929.38670531982007</v>
       </c>
       <c r="CI18" s="16">
         <f t="shared" si="33"/>
-        <v>931.77654359116571</v>
+        <v>920.09283826662181</v>
       </c>
       <c r="CJ18" s="16">
         <f t="shared" si="33"/>
-        <v>922.45877815525409</v>
+        <v>910.89190988395558</v>
       </c>
       <c r="CK18" s="16">
         <f t="shared" si="33"/>
-        <v>913.23419037370149</v>
+        <v>901.782990785116</v>
       </c>
       <c r="CL18" s="16">
         <f t="shared" si="33"/>
-        <v>904.10184846996447</v>
+        <v>892.76516087726486</v>
       </c>
       <c r="CM18" s="16">
         <f t="shared" si="33"/>
-        <v>895.06082998526483</v>
+        <v>883.83750926849223</v>
       </c>
       <c r="CN18" s="16">
         <f t="shared" si="33"/>
-        <v>886.11022168541217</v>
+        <v>874.99913417580728</v>
       </c>
       <c r="CO18" s="16">
         <f t="shared" si="33"/>
-        <v>877.24911946855809</v>
+        <v>866.24914283404917</v>
       </c>
       <c r="CP18" s="16">
         <f t="shared" si="33"/>
-        <v>868.47662827387251</v>
+        <v>857.58665140570872</v>
       </c>
       <c r="CQ18" s="16">
         <f t="shared" si="33"/>
-        <v>859.79186199113383</v>
+        <v>849.01078489165161</v>
       </c>
       <c r="CR18" s="16">
         <f t="shared" si="33"/>
-        <v>851.19394337122253</v>
+        <v>840.52067704273509</v>
       </c>
       <c r="CS18" s="16">
         <f t="shared" si="33"/>
-        <v>842.68200393751033</v>
+        <v>832.11547027230768</v>
       </c>
       <c r="CT18" s="16">
         <f t="shared" si="33"/>
-        <v>834.25518389813521</v>
+        <v>823.79431556958457</v>
       </c>
       <c r="CU18" s="16">
         <f t="shared" si="33"/>
-        <v>825.91263205915391</v>
+        <v>815.55637241388877</v>
       </c>
       <c r="CV18" s="16">
         <f t="shared" si="33"/>
-        <v>817.65350573856233</v>
+        <v>807.40080868974985</v>
       </c>
       <c r="CW18" s="16">
         <f t="shared" si="33"/>
-        <v>809.47697068117668</v>
+        <v>799.32680060285236</v>
       </c>
       <c r="CX18" s="16">
         <f t="shared" si="33"/>
-        <v>801.38220097436488</v>
+        <v>791.33353259682383</v>
       </c>
       <c r="CY18" s="16">
         <f t="shared" si="33"/>
-        <v>793.36837896462123</v>
+        <v>783.42019727085562</v>
       </c>
       <c r="CZ18" s="16">
         <f t="shared" si="33"/>
-        <v>785.43469517497499</v>
+        <v>775.58599529814705</v>
       </c>
       <c r="DA18" s="16">
         <f t="shared" si="33"/>
-        <v>777.5803482232252</v>
+        <v>767.83013534516556</v>
       </c>
       <c r="DB18" s="16">
         <f t="shared" si="33"/>
-        <v>769.80454474099292</v>
+        <v>760.15183399171394</v>
       </c>
       <c r="DC18" s="16">
         <f t="shared" si="33"/>
-        <v>762.10649929358294</v>
+        <v>752.55031565179684</v>
       </c>
       <c r="DD18" s="16">
         <f t="shared" ref="DD18:FO18" si="34">DC18*(1+$AS$22)</f>
-        <v>754.48543430064706</v>
+        <v>745.02481249527887</v>
       </c>
       <c r="DE18" s="16">
         <f t="shared" si="34"/>
-        <v>746.94057995764058</v>
+        <v>737.57456437032602</v>
       </c>
       <c r="DF18" s="16">
         <f t="shared" si="34"/>
-        <v>739.47117415806417</v>
+        <v>730.19881872662279</v>
       </c>
       <c r="DG18" s="16">
         <f t="shared" si="34"/>
-        <v>732.07646241648354</v>
+        <v>722.89683053935653</v>
       </c>
       <c r="DH18" s="16">
         <f t="shared" si="34"/>
-        <v>724.75569779231864</v>
+        <v>715.66786223396298</v>
       </c>
       <c r="DI18" s="16">
         <f t="shared" si="34"/>
-        <v>717.50814081439546</v>
+        <v>708.51118361162332</v>
       </c>
       <c r="DJ18" s="16">
         <f t="shared" si="34"/>
-        <v>710.33305940625155</v>
+        <v>701.42607177550713</v>
       </c>
       <c r="DK18" s="16">
         <f t="shared" si="34"/>
-        <v>703.22972881218902</v>
+        <v>694.41181105775206</v>
       </c>
       <c r="DL18" s="16">
         <f t="shared" si="34"/>
-        <v>696.19743152406716</v>
+        <v>687.46769294717456</v>
       </c>
       <c r="DM18" s="16">
         <f t="shared" si="34"/>
-        <v>689.23545720882646</v>
+        <v>680.59301601770278</v>
       </c>
       <c r="DN18" s="16">
         <f t="shared" si="34"/>
-        <v>682.34310263673819</v>
+        <v>673.78708585752577</v>
       </c>
       <c r="DO18" s="16">
         <f t="shared" si="34"/>
-        <v>675.51967161037078</v>
+        <v>667.04921499895045</v>
       </c>
       <c r="DP18" s="16">
         <f t="shared" si="34"/>
-        <v>668.7644748942671</v>
+        <v>660.37872284896093</v>
       </c>
       <c r="DQ18" s="16">
         <f t="shared" si="34"/>
-        <v>662.07683014532438</v>
+        <v>653.7749356204713</v>
       </c>
       <c r="DR18" s="16">
         <f t="shared" si="34"/>
-        <v>655.45606184387111</v>
+        <v>647.2371862642666</v>
       </c>
       <c r="DS18" s="16">
         <f t="shared" si="34"/>
-        <v>648.90150122543241</v>
+        <v>640.76481440162388</v>
       </c>
       <c r="DT18" s="16">
         <f t="shared" si="34"/>
-        <v>642.41248621317811</v>
+        <v>634.35716625760767</v>
       </c>
       <c r="DU18" s="16">
         <f t="shared" si="34"/>
-        <v>635.98836135104636</v>
+        <v>628.01359459503158</v>
       </c>
       <c r="DV18" s="16">
         <f t="shared" si="34"/>
-        <v>629.62847773753595</v>
+        <v>621.73345864908129</v>
       </c>
       <c r="DW18" s="16">
         <f t="shared" si="34"/>
-        <v>623.33219296016057</v>
+        <v>615.51612406259051</v>
       </c>
       <c r="DX18" s="16">
         <f t="shared" si="34"/>
-        <v>617.09887103055894</v>
+        <v>609.36096282196456</v>
       </c>
       <c r="DY18" s="16">
         <f t="shared" si="34"/>
-        <v>610.92788232025339</v>
+        <v>603.26735319374495</v>
       </c>
       <c r="DZ18" s="16">
         <f t="shared" si="34"/>
-        <v>604.81860349705084</v>
+        <v>597.23467966180749</v>
       </c>
       <c r="EA18" s="16">
         <f t="shared" si="34"/>
-        <v>598.77041746208033</v>
+        <v>591.26233286518936</v>
       </c>
       <c r="EB18" s="16">
         <f t="shared" si="34"/>
-        <v>592.7827132874595</v>
+        <v>585.34970953653749</v>
       </c>
       <c r="EC18" s="16">
         <f t="shared" si="34"/>
-        <v>586.85488615458485</v>
+        <v>579.49621244117213</v>
       </c>
       <c r="ED18" s="16">
         <f t="shared" si="34"/>
-        <v>580.98633729303901</v>
+        <v>573.70125031676037</v>
       </c>
       <c r="EE18" s="16">
         <f t="shared" si="34"/>
-        <v>575.17647392010861</v>
+        <v>567.96423781359272</v>
       </c>
       <c r="EF18" s="16">
         <f t="shared" si="34"/>
-        <v>569.42470918090748</v>
+        <v>562.28459543545682</v>
       </c>
       <c r="EG18" s="16">
         <f t="shared" si="34"/>
-        <v>563.73046208909841</v>
+        <v>556.66174948110222</v>
       </c>
       <c r="EH18" s="16">
         <f t="shared" si="34"/>
-        <v>558.09315746820744</v>
+        <v>551.09513198629122</v>
       </c>
       <c r="EI18" s="16">
         <f t="shared" si="34"/>
-        <v>552.5122258935254</v>
+        <v>545.58418066642832</v>
       </c>
       <c r="EJ18" s="16">
         <f t="shared" si="34"/>
-        <v>546.98710363459008</v>
+        <v>540.12833885976409</v>
       </c>
       <c r="EK18" s="16">
         <f t="shared" si="34"/>
-        <v>541.51723259824416</v>
+        <v>534.72705547116641</v>
       </c>
       <c r="EL18" s="16">
         <f t="shared" si="34"/>
-        <v>536.10206027226172</v>
+        <v>529.3797849164547</v>
       </c>
       <c r="EM18" s="16">
         <f t="shared" si="34"/>
-        <v>530.74103966953908</v>
+        <v>524.08598706729015</v>
       </c>
       <c r="EN18" s="16">
         <f t="shared" si="34"/>
-        <v>525.43362927284363</v>
+        <v>518.84512719661723</v>
       </c>
       <c r="EO18" s="16">
         <f t="shared" si="34"/>
-        <v>520.17929298011518</v>
+        <v>513.65667592465104</v>
       </c>
       <c r="EP18" s="16">
         <f t="shared" si="34"/>
-        <v>514.97750005031401</v>
+        <v>508.52010916540451</v>
       </c>
       <c r="EQ18" s="16">
         <f t="shared" si="34"/>
-        <v>509.82772504981085</v>
+        <v>503.43490807375048</v>
       </c>
       <c r="ER18" s="16">
         <f t="shared" si="34"/>
-        <v>504.72944779931277</v>
+        <v>498.40055899301296</v>
       </c>
       <c r="ES18" s="16">
         <f t="shared" si="34"/>
-        <v>499.68215332131962</v>
+        <v>493.41655340308284</v>
       </c>
       <c r="ET18" s="16">
         <f t="shared" si="34"/>
-        <v>494.6853317881064</v>
+        <v>488.48238786905199</v>
       </c>
       <c r="EU18" s="16">
         <f t="shared" si="34"/>
-        <v>489.73847847022535</v>
+        <v>483.59756399036149</v>
       </c>
       <c r="EV18" s="16">
         <f t="shared" si="34"/>
-        <v>484.84109368552311</v>
+        <v>478.76158835045788</v>
       </c>
       <c r="EW18" s="16">
         <f t="shared" si="34"/>
-        <v>479.99268274866785</v>
+        <v>473.97397246695328</v>
       </c>
       <c r="EX18" s="16">
         <f t="shared" si="34"/>
-        <v>475.19275592118117</v>
+        <v>469.23423274228372</v>
       </c>
       <c r="EY18" s="16">
         <f t="shared" si="34"/>
-        <v>470.44082836196935</v>
+        <v>464.54189041486086</v>
       </c>
       <c r="EZ18" s="16">
         <f t="shared" si="34"/>
-        <v>465.73642007834968</v>
+        <v>459.89647151071227</v>
       </c>
       <c r="FA18" s="16">
         <f t="shared" si="34"/>
-        <v>461.07905587756619</v>
+        <v>455.29750679560516</v>
       </c>
       <c r="FB18" s="16">
         <f t="shared" si="34"/>
-        <v>456.46826531879054</v>
+        <v>450.74453172764908</v>
       </c>
       <c r="FC18" s="16">
         <f t="shared" si="34"/>
-        <v>451.90358266560264</v>
+        <v>446.23708641037257</v>
       </c>
       <c r="FD18" s="16">
         <f t="shared" si="34"/>
-        <v>447.38454683894662</v>
+        <v>441.77471554626885</v>
       </c>
       <c r="FE18" s="16">
         <f t="shared" si="34"/>
-        <v>442.91070137055715</v>
+        <v>437.35696839080617</v>
       </c>
       <c r="FF18" s="16">
         <f t="shared" si="34"/>
-        <v>438.48159435685159</v>
+        <v>432.98339870689813</v>
       </c>
       <c r="FG18" s="16">
         <f t="shared" si="34"/>
-        <v>434.09677841328306</v>
+        <v>428.65356471982915</v>
       </c>
       <c r="FH18" s="16">
         <f t="shared" si="34"/>
-        <v>429.75581062915023</v>
+        <v>424.36702907263083</v>
       </c>
       <c r="FI18" s="16">
         <f t="shared" si="34"/>
-        <v>425.45825252285874</v>
+        <v>420.12335878190453</v>
       </c>
       <c r="FJ18" s="16">
         <f t="shared" si="34"/>
-        <v>421.20366999763013</v>
+        <v>415.92212519408548</v>
       </c>
       <c r="FK18" s="16">
         <f t="shared" si="34"/>
-        <v>416.99163329765383</v>
+        <v>411.76290394214465</v>
       </c>
       <c r="FL18" s="16">
         <f t="shared" si="34"/>
-        <v>412.82171696467731</v>
+        <v>407.6452749027232</v>
       </c>
       <c r="FM18" s="16">
         <f t="shared" si="34"/>
-        <v>408.6934997950305</v>
+        <v>403.56882215369598</v>
       </c>
       <c r="FN18" s="16">
         <f t="shared" si="34"/>
-        <v>404.60656479708018</v>
+        <v>399.53313393215899</v>
       </c>
       <c r="FO18" s="16">
         <f t="shared" si="34"/>
-        <v>400.56049914910938</v>
+        <v>395.53780259283741</v>
       </c>
       <c r="FP18" s="16">
         <f t="shared" ref="FP18:GX18" si="35">FO18*(1+$AS$22)</f>
-        <v>396.55489415761826</v>
+        <v>391.58242456690903</v>
       </c>
       <c r="FQ18" s="16">
         <f t="shared" si="35"/>
-        <v>392.58934521604209</v>
+        <v>387.66660032123991</v>
       </c>
       <c r="FR18" s="16">
         <f t="shared" si="35"/>
-        <v>388.66345176388165</v>
+        <v>383.78993431802752</v>
       </c>
       <c r="FS18" s="16">
         <f t="shared" si="35"/>
-        <v>384.77681724624284</v>
+        <v>379.95203497484727</v>
       </c>
       <c r="FT18" s="16">
         <f t="shared" si="35"/>
-        <v>380.92904907378039</v>
+        <v>376.15251462509877</v>
       </c>
       <c r="FU18" s="16">
         <f t="shared" si="35"/>
-        <v>377.1197585830426</v>
+        <v>372.39098947884776</v>
       </c>
       <c r="FV18" s="16">
         <f t="shared" si="35"/>
-        <v>373.34856099721219</v>
+        <v>368.66707958405925</v>
       </c>
       <c r="FW18" s="16">
         <f t="shared" si="35"/>
-        <v>369.61507538724004</v>
+        <v>364.98040878821865</v>
       </c>
       <c r="FX18" s="16">
         <f t="shared" si="35"/>
-        <v>365.91892463336762</v>
+        <v>361.33060470033644</v>
       </c>
       <c r="FY18" s="16">
         <f t="shared" si="35"/>
-        <v>362.25973538703397</v>
+        <v>357.71729865333305</v>
       </c>
       <c r="FZ18" s="16">
         <f t="shared" si="35"/>
-        <v>358.63713803316364</v>
+        <v>354.14012566679969</v>
       </c>
       <c r="GA18" s="16">
         <f t="shared" si="35"/>
-        <v>355.05076665283201</v>
+        <v>350.59872441013169</v>
       </c>
       <c r="GB18" s="16">
         <f t="shared" si="35"/>
-        <v>351.50025898630366</v>
+        <v>347.09273716603036</v>
       </c>
       <c r="GC18" s="16">
         <f t="shared" si="35"/>
-        <v>347.9852563964406</v>
+        <v>343.62180979437005</v>
       </c>
       <c r="GD18" s="16">
         <f t="shared" si="35"/>
-        <v>344.50540383247619</v>
+        <v>340.18559169642634</v>
       </c>
       <c r="GE18" s="16">
         <f t="shared" si="35"/>
-        <v>341.06034979415142</v>
+        <v>336.78373577946206</v>
       </c>
       <c r="GF18" s="16">
         <f t="shared" si="35"/>
-        <v>337.64974629620991</v>
+        <v>333.41589842166746</v>
       </c>
       <c r="GG18" s="16">
         <f t="shared" si="35"/>
-        <v>334.27324883324781</v>
+        <v>330.08173943745078</v>
       </c>
       <c r="GH18" s="16">
         <f t="shared" si="35"/>
-        <v>330.9305163449153</v>
+        <v>326.78092204307626</v>
       </c>
       <c r="GI18" s="16">
         <f t="shared" si="35"/>
-        <v>327.62121118146615</v>
+        <v>323.5131128226455</v>
       </c>
       <c r="GJ18" s="16">
         <f t="shared" si="35"/>
-        <v>324.34499906965146</v>
+        <v>320.27798169441905</v>
       </c>
       <c r="GK18" s="16">
         <f t="shared" si="35"/>
-        <v>321.10154907895497</v>
+        <v>317.07520187747485</v>
       </c>
       <c r="GL18" s="16">
         <f t="shared" si="35"/>
-        <v>317.8905335881654</v>
+        <v>313.9044498587001</v>
       </c>
       <c r="GM18" s="16">
         <f t="shared" si="35"/>
-        <v>314.71162825228373</v>
+        <v>310.76540536011311</v>
       </c>
       <c r="GN18" s="16">
         <f t="shared" si="35"/>
-        <v>311.56451196976087</v>
+        <v>307.65775130651195</v>
       </c>
       <c r="GO18" s="16">
         <f t="shared" si="35"/>
-        <v>308.44886685006327</v>
+        <v>304.58117379344685</v>
       </c>
       <c r="GP18" s="16">
         <f t="shared" si="35"/>
-        <v>305.36437818156264</v>
+        <v>301.53536205551239</v>
       </c>
       <c r="GQ18" s="16">
         <f t="shared" si="35"/>
-        <v>302.31073439974699</v>
+        <v>298.52000843495728</v>
       </c>
       <c r="GR18" s="16">
         <f t="shared" si="35"/>
-        <v>299.28762705574951</v>
+        <v>295.5348083506077</v>
       </c>
       <c r="GS18" s="16">
         <f t="shared" si="35"/>
-        <v>296.29475078519204</v>
+        <v>292.57946026710164</v>
       </c>
       <c r="GT18" s="16">
         <f t="shared" si="35"/>
-        <v>293.3318032773401</v>
+        <v>289.6536656644306</v>
       </c>
       <c r="GU18" s="16">
         <f t="shared" si="35"/>
-        <v>290.3984852445667</v>
+        <v>286.75712900778632</v>
       </c>
       <c r="GV18" s="16">
         <f t="shared" si="35"/>
-        <v>287.49450039212104</v>
+        <v>283.88955771770844</v>
       </c>
       <c r="GW18" s="16">
         <f t="shared" si="35"/>
-        <v>284.61955538819984</v>
+        <v>281.05066214053136</v>
       </c>
       <c r="GX18" s="16">
         <f t="shared" si="35"/>
-        <v>281.77335983431783</v>
-      </c>
-    </row>
-    <row r="19" spans="1:206" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="42"/>
+        <v>278.24015551912606</v>
+      </c>
+    </row>
+    <row r="19" spans="1:206" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="41"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="29">
         <v>147.6</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="29">
         <v>146.64874800000001</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="29">
         <v>147.82344599999999</v>
       </c>
-      <c r="O19" s="30">
+      <c r="O19" s="29">
         <v>146.64874800000001</v>
       </c>
-      <c r="P19" s="30">
+      <c r="P19" s="29">
         <v>144.51324199999999</v>
       </c>
-      <c r="Q19" s="30">
+      <c r="Q19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="R19" s="30">
+      <c r="R19" s="29">
         <v>143.9736</v>
       </c>
-      <c r="S19" s="30">
+      <c r="S19" s="29">
         <v>142.81814</v>
       </c>
       <c r="T19" s="8">
         <v>141.96249399999999</v>
       </c>
-      <c r="AA19" s="30">
+      <c r="AA19" s="29">
         <v>37.181941999999999</v>
       </c>
-      <c r="AB19" s="30">
+      <c r="AB19" s="29">
         <v>150</v>
       </c>
-      <c r="AC19" s="30">
+      <c r="AC19" s="29">
         <v>149.05500000000001</v>
       </c>
-      <c r="AD19" s="30">
+      <c r="AD19" s="29">
         <v>147.423677</v>
       </c>
-      <c r="AE19" s="30">
+      <c r="AE19" s="29">
         <v>146.64874800000001</v>
       </c>
-      <c r="AF19" s="30">
+      <c r="AF19" s="29">
         <v>142.81814</v>
       </c>
       <c r="AG19" s="8">
         <v>141.96249399999999</v>
       </c>
-      <c r="AH19" s="30">
+      <c r="AH19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AI19" s="30">
+      <c r="AI19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AJ19" s="30">
+      <c r="AJ19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AK19" s="30">
+      <c r="AK19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AL19" s="30">
+      <c r="AL19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AM19" s="30">
+      <c r="AM19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AN19" s="30">
+      <c r="AN19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AO19" s="30">
+      <c r="AO19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="AP19" s="30">
+      <c r="AP19" s="29">
         <v>141.96249399999999</v>
       </c>
     </row>
@@ -5223,139 +5275,139 @@
       <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="31" t="e">
+      <c r="D20" s="30" t="e">
         <f t="shared" ref="D20:R20" si="36">D18/D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="31" t="e">
+      <c r="E20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F20" s="31" t="e">
+      <c r="F20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G20" s="31" t="e">
+      <c r="G20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="31" t="e">
+      <c r="H20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I20" s="31" t="e">
+      <c r="I20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J20" s="31" t="e">
+      <c r="J20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="31" t="e">
+      <c r="K20" s="30" t="e">
         <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="30">
         <f t="shared" si="36"/>
         <v>0.38617886178861788</v>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="30">
         <f t="shared" si="36"/>
         <v>1.1455945058596748</v>
       </c>
-      <c r="N20" s="31">
+      <c r="N20" s="30">
         <f t="shared" si="36"/>
         <v>0.44647856470616987</v>
       </c>
-      <c r="O20" s="31">
+      <c r="O20" s="30">
         <f t="shared" si="36"/>
         <v>0.51824513360318625</v>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="30">
         <f t="shared" si="36"/>
         <v>0.60202095528380717</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="30">
         <f t="shared" si="36"/>
         <v>0.79821792945910097</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="30">
         <f t="shared" si="36"/>
         <v>0.90294331738596523</v>
       </c>
-      <c r="S20" s="31">
+      <c r="S20" s="30">
         <f>S18/S19</f>
         <v>0.85423322275447644</v>
       </c>
-      <c r="T20" s="40">
+      <c r="T20" s="39">
         <f>T18/T19</f>
         <v>0.91573482782008608</v>
       </c>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="AA20" s="31">
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="AA20" s="30">
         <f t="shared" ref="AA20:AE20" si="37">AA18/AA19</f>
         <v>-5.2444813129986594</v>
       </c>
-      <c r="AB20" s="31">
+      <c r="AB20" s="30">
         <f t="shared" si="37"/>
         <v>0.34</v>
       </c>
-      <c r="AC20" s="31">
+      <c r="AC20" s="30">
         <f t="shared" si="37"/>
         <v>2.2005300057025927</v>
       </c>
-      <c r="AD20" s="31">
+      <c r="AD20" s="30">
         <f t="shared" si="37"/>
         <v>2.1095661587656642</v>
       </c>
-      <c r="AE20" s="31">
+      <c r="AE20" s="30">
         <f t="shared" si="37"/>
         <v>2.4957594591942915</v>
       </c>
-      <c r="AF20" s="31">
+      <c r="AF20" s="30">
         <f>AF18/AF19</f>
         <v>3.1788678945125599</v>
       </c>
-      <c r="AG20" s="40">
+      <c r="AG20" s="39">
         <f t="shared" ref="AG20:AP20" si="38">AG18/AG19</f>
-        <v>3.7549072644497206</v>
-      </c>
-      <c r="AH20" s="31">
+        <v>3.6422014394872484</v>
+      </c>
+      <c r="AH20" s="30">
         <f t="shared" si="38"/>
-        <v>4.1678591529957174</v>
-      </c>
-      <c r="AI20" s="31">
+        <v>4.0483909785354966</v>
+      </c>
+      <c r="AI20" s="30">
         <f t="shared" si="38"/>
-        <v>4.8749455303314155</v>
-      </c>
-      <c r="AJ20" s="31">
+        <v>4.7542826741265936</v>
+      </c>
+      <c r="AJ20" s="30">
         <f t="shared" si="38"/>
-        <v>5.511716309858584</v>
-      </c>
-      <c r="AK20" s="31">
+        <v>5.3898468250917126</v>
+      </c>
+      <c r="AK20" s="30">
         <f t="shared" si="38"/>
-        <v>6.1907867241520975</v>
-      </c>
-      <c r="AL20" s="31">
+        <v>6.0676985445375573</v>
+      </c>
+      <c r="AL20" s="30">
         <f t="shared" si="38"/>
-        <v>6.9147486981282285</v>
-      </c>
-      <c r="AM20" s="31">
+        <v>6.7904296367175432</v>
+      </c>
+      <c r="AM20" s="30">
         <f t="shared" si="38"/>
-        <v>7.6863504719255715</v>
-      </c>
-      <c r="AN20" s="31">
+        <v>7.5607882199007808</v>
+      </c>
+      <c r="AN20" s="30">
         <f t="shared" si="38"/>
-        <v>8.5085059930207585</v>
-      </c>
-      <c r="AO20" s="31">
+        <v>8.3816881184757186</v>
+      </c>
+      <c r="AO20" s="30">
         <f t="shared" si="38"/>
-        <v>9.3843048721073679</v>
-      </c>
-      <c r="AP20" s="31">
+        <v>9.2562188188168761</v>
+      </c>
+      <c r="AP20" s="30">
         <f t="shared" si="38"/>
-        <v>10.317022936568126</v>
+        <v>10.187656022744733</v>
       </c>
     </row>
     <row r="21" spans="1:206" x14ac:dyDescent="0.25">
@@ -5373,13 +5425,13 @@
       <c r="AR21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AS21" s="36">
+      <c r="AS21" s="35">
         <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="1:206" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="32"/>
+      <c r="B22" s="31"/>
       <c r="C22" s="14" t="s">
         <v>33</v>
       </c>
@@ -5431,7 +5483,7 @@
         <f>(S4-O4)/O4</f>
         <v>0.10548523206751055</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="31">
         <f>(T4-P4)/P4</f>
         <v>3.804034582132565E-2</v>
       </c>
@@ -5455,7 +5507,7 @@
         <f>(AF4-AE4)/AE4</f>
         <v>0.10395584176632934</v>
       </c>
-      <c r="AG22" s="32">
+      <c r="AG22" s="31">
         <f t="shared" ref="AG22:AP22" si="41">(AG4-AF4)/AF4</f>
         <v>0.06</v>
       </c>
@@ -5498,12 +5550,12 @@
       <c r="AR22" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AS22" s="36">
+      <c r="AS22" s="35">
         <v>-0.01</v>
       </c>
     </row>
     <row r="23" spans="1:206" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="27"/>
+      <c r="B23" s="26"/>
       <c r="C23" s="13" t="s">
         <v>109</v>
       </c>
@@ -5555,7 +5607,7 @@
       <c r="S23" s="13">
         <v>0.114</v>
       </c>
-      <c r="T23" s="27">
+      <c r="T23" s="26">
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="AA23" s="13">
@@ -5576,17 +5628,20 @@
       <c r="AF23" s="13">
         <v>0.114</v>
       </c>
-      <c r="AG23" s="27"/>
-      <c r="AR23" s="35" t="s">
+      <c r="AG23" s="26">
+        <f>(AG13/AF13)-1</f>
+        <v>7.1647331786542701E-2</v>
+      </c>
+      <c r="AR23" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="AS23" s="37">
+      <c r="AS23" s="36">
         <f>NPV(AS21,AG18:GX18)</f>
-        <v>13438.67942358883</v>
+        <v>13228.691749260979</v>
       </c>
     </row>
     <row r="24" spans="1:206" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="32"/>
+      <c r="B24" s="31"/>
       <c r="C24" s="14" t="s">
         <v>111</v>
       </c>
@@ -5638,10 +5693,10 @@
       <c r="S24" s="14">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="31">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="AG24" s="32"/>
+      <c r="AG24" s="31"/>
       <c r="AR24" s="13" t="s">
         <v>2</v>
       </c>
@@ -5667,7 +5722,7 @@
       <c r="Q25" s="14"/>
       <c r="R25" s="14"/>
       <c r="S25" s="14"/>
-      <c r="T25" s="32"/>
+      <c r="T25" s="31"/>
       <c r="U25" s="14"/>
       <c r="V25" s="14"/>
       <c r="W25" s="14"/>
@@ -5680,7 +5735,7 @@
       <c r="AD25" s="14"/>
       <c r="AE25" s="14"/>
       <c r="AF25" s="14"/>
-      <c r="AG25" s="32"/>
+      <c r="AG25" s="31"/>
       <c r="AH25" s="14"/>
       <c r="AI25" s="14"/>
       <c r="AJ25" s="14"/>
@@ -5693,9 +5748,9 @@
       <c r="AR25" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AS25" s="38">
+      <c r="AS25" s="37">
         <f>AS23/AS24</f>
-        <v>94.663590677611168</v>
+        <v>93.184413548419201</v>
       </c>
     </row>
     <row r="26" spans="1:206" x14ac:dyDescent="0.25">
@@ -5766,7 +5821,7 @@
         <f t="shared" si="42"/>
         <v>0.7715376226826608</v>
       </c>
-      <c r="T26" s="27">
+      <c r="T26" s="26">
         <f t="shared" ref="T26" si="43">T6/T4</f>
         <v>0.76179900055524707</v>
       </c>
@@ -5800,7 +5855,7 @@
         <f t="shared" si="44"/>
         <v>0.74708333333333332</v>
       </c>
-      <c r="AG26" s="27">
+      <c r="AG26" s="26">
         <f t="shared" si="44"/>
         <v>0.76</v>
       </c>
@@ -5845,7 +5900,7 @@
       </c>
       <c r="AS26" s="14">
         <f>(AS25-B4)/B4</f>
-        <v>0.74013953451491121</v>
+        <v>0.6942620645167128</v>
       </c>
     </row>
     <row r="27" spans="1:206" x14ac:dyDescent="0.25">
@@ -5916,7 +5971,7 @@
         <f t="shared" si="45"/>
         <v>0.23227917121046893</v>
       </c>
-      <c r="T27" s="27">
+      <c r="T27" s="26">
         <f t="shared" ref="T27" si="46">T9/T4</f>
         <v>0.2220988339811216</v>
       </c>
@@ -5944,7 +5999,7 @@
         <f t="shared" si="47"/>
         <v>0.23444444444444446</v>
       </c>
-      <c r="AG27" s="27">
+      <c r="AG27" s="26">
         <f t="shared" si="47"/>
         <v>0.245251572327044</v>
       </c>
@@ -6053,7 +6108,7 @@
         <f t="shared" si="48"/>
         <v>0.13413304252998909</v>
       </c>
-      <c r="T28" s="27">
+      <c r="T28" s="26">
         <f t="shared" ref="T28" si="49">T11/T4</f>
         <v>0.12104386451971128</v>
       </c>
@@ -6081,45 +6136,45 @@
         <f t="shared" si="50"/>
         <v>0.13694444444444445</v>
       </c>
-      <c r="AG28" s="27">
+      <c r="AG28" s="26">
         <f t="shared" si="50"/>
-        <v>0.1404297693920335</v>
+        <v>0.13780922431865825</v>
       </c>
       <c r="AH28" s="13">
         <f t="shared" si="50"/>
-        <v>0.14285782801313232</v>
+        <v>0.14023728293975707</v>
       </c>
       <c r="AI28" s="13">
         <f t="shared" si="50"/>
-        <v>0.15021885819427377</v>
+        <v>0.14772192373756715</v>
       </c>
       <c r="AJ28" s="13">
         <f t="shared" si="50"/>
-        <v>0.15493005528239956</v>
+        <v>0.1525509007528961</v>
       </c>
       <c r="AK28" s="13">
         <f t="shared" si="50"/>
-        <v>0.15941902609278349</v>
+        <v>0.15715209583353962</v>
       </c>
       <c r="AL28" s="13">
         <f t="shared" si="50"/>
-        <v>0.16369625299701709</v>
+        <v>0.16153625341037905</v>
       </c>
       <c r="AM28" s="13">
         <f t="shared" si="50"/>
-        <v>0.16777172391520215</v>
+        <v>0.16571361110151875</v>
       </c>
       <c r="AN28" s="13">
         <f t="shared" si="50"/>
-        <v>0.17165495563913313</v>
+        <v>0.16969392361854799</v>
       </c>
       <c r="AO28" s="13">
         <f t="shared" si="50"/>
-        <v>0.17535501605533141</v>
+        <v>0.17348648554515123</v>
       </c>
       <c r="AP28" s="13">
         <f t="shared" si="50"/>
-        <v>0.17888054531982245</v>
+        <v>0.17710015304125457</v>
       </c>
     </row>
     <row r="29" spans="1:206" x14ac:dyDescent="0.25">
@@ -6190,7 +6245,7 @@
         <f t="shared" si="51"/>
         <v>0.11668484187568157</v>
       </c>
-      <c r="T29" s="27">
+      <c r="T29" s="26">
         <f t="shared" ref="T29" si="52">T13/T4</f>
         <v>0.10327595780122155</v>
       </c>
@@ -6224,49 +6279,49 @@
         <f t="shared" si="53"/>
         <v>0.11972222222222222</v>
       </c>
-      <c r="AG29" s="27">
+      <c r="AG29" s="26">
         <f t="shared" si="53"/>
-        <v>0.12365828092243183</v>
+        <v>0.12103773584905657</v>
       </c>
       <c r="AH29" s="13">
         <f t="shared" si="53"/>
-        <v>0.12640278272220237</v>
+        <v>0.12378223764882712</v>
       </c>
       <c r="AI29" s="13">
         <f t="shared" si="53"/>
-        <v>0.13453999428499147</v>
+        <v>0.13204305982828485</v>
       </c>
       <c r="AJ29" s="13">
         <f t="shared" si="53"/>
-        <v>0.1399907604254419</v>
+        <v>0.13761160589593843</v>
       </c>
       <c r="AK29" s="13">
         <f t="shared" si="53"/>
-        <v>0.14518441495549367</v>
+        <v>0.14291748469624979</v>
       </c>
       <c r="AL29" s="13">
         <f t="shared" si="53"/>
-        <v>0.1501330857812975</v>
+        <v>0.14797308619465949</v>
       </c>
       <c r="AM29" s="13">
         <f t="shared" si="53"/>
-        <v>0.15484832873795989</v>
+        <v>0.1527902159242765</v>
       </c>
       <c r="AN29" s="13">
         <f t="shared" si="53"/>
-        <v>0.15934115457402495</v>
+        <v>0.15738012255343981</v>
       </c>
       <c r="AO29" s="13">
         <f t="shared" si="53"/>
-        <v>0.16362205466310567</v>
+        <v>0.16175352415292552</v>
       </c>
       <c r="AP29" s="13">
         <f t="shared" si="53"/>
-        <v>0.16770102550270174</v>
+        <v>0.16592063322413386</v>
       </c>
     </row>
     <row r="30" spans="1:206" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="13" t="s">
         <v>37</v>
       </c>
@@ -6302,7 +6357,7 @@
       <c r="AP30" s="2"/>
     </row>
     <row r="31" spans="1:206" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="27"/>
+      <c r="B31" s="26"/>
       <c r="T31" s="3"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
@@ -6391,7 +6446,7 @@
       </c>
     </row>
     <row r="33" spans="2:42" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="27"/>
+      <c r="B33" s="26"/>
       <c r="C33" s="13" t="s">
         <v>149</v>
       </c>
@@ -6455,14 +6510,14 @@
         <f t="shared" si="54"/>
         <v>2.0242914979757085E-2</v>
       </c>
-      <c r="T33" s="27">
+      <c r="T33" s="26">
         <f>(T32-S32)/S32</f>
         <v>1.8518518518518517E-2</v>
       </c>
-      <c r="AG33" s="27"/>
+      <c r="AG33" s="26"/>
     </row>
     <row r="34" spans="2:42" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="13" t="s">
         <v>148</v>
       </c>
@@ -6514,11 +6569,11 @@
       <c r="S34" s="13">
         <v>2.9700000000000001E-2</v>
       </c>
-      <c r="T34" s="27">
+      <c r="T34" s="26">
         <v>3.04E-2</v>
       </c>
       <c r="AD34" s="13">
-        <f t="shared" ref="AC34:AE34" si="55">(AD32-AC32)/AC32</f>
+        <f t="shared" ref="AD34:AE34" si="55">(AD32-AC32)/AC32</f>
         <v>0.21330724070450097</v>
       </c>
       <c r="AE34" s="13">
@@ -6529,198 +6584,198 @@
         <f>(AF32-AE32)/AE32</f>
         <v>7.5391180654338544E-2</v>
       </c>
-      <c r="AG34" s="27"/>
+      <c r="AG34" s="26"/>
     </row>
     <row r="35" spans="2:42" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="27"/>
-      <c r="C35" s="68" t="s">
+      <c r="B35" s="26"/>
+      <c r="C35" s="67" t="s">
         <v>150</v>
       </c>
-      <c r="E35" s="69">
+      <c r="E35" s="68">
         <f>-E34*D32</f>
         <v>-8.8827999999999996</v>
       </c>
-      <c r="F35" s="69">
+      <c r="F35" s="68">
         <f t="shared" ref="F35:R35" si="56">-F34*E32</f>
         <v>-9.7432999999999996</v>
       </c>
-      <c r="G35" s="69">
+      <c r="G35" s="68">
         <f t="shared" si="56"/>
         <v>-10.085800000000001</v>
       </c>
-      <c r="H35" s="69">
+      <c r="H35" s="68">
         <f t="shared" si="56"/>
         <v>-11.088700000000001</v>
       </c>
-      <c r="I35" s="69">
+      <c r="I35" s="68">
         <f t="shared" si="56"/>
         <v>-10.081199999999999</v>
       </c>
-      <c r="J35" s="69">
+      <c r="J35" s="68">
         <f t="shared" si="56"/>
         <v>-11.668800000000001</v>
       </c>
-      <c r="K35" s="69">
+      <c r="K35" s="68">
         <f t="shared" si="56"/>
         <v>-13.566000000000001</v>
       </c>
-      <c r="L35" s="69">
+      <c r="L35" s="68">
         <f t="shared" si="56"/>
         <v>-14.446000000000002</v>
       </c>
-      <c r="M35" s="69">
+      <c r="M35" s="68">
         <f t="shared" si="56"/>
         <v>-16.189499999999999</v>
       </c>
-      <c r="N35" s="69">
+      <c r="N35" s="68">
         <f t="shared" si="56"/>
         <v>-17.341999999999999</v>
       </c>
-      <c r="O35" s="69">
+      <c r="O35" s="68">
         <f t="shared" si="56"/>
         <v>-18.372700000000002</v>
       </c>
-      <c r="P35" s="69">
+      <c r="P35" s="68">
         <f t="shared" si="56"/>
         <v>-19.965199999999999</v>
       </c>
-      <c r="Q35" s="69">
+      <c r="Q35" s="68">
         <f t="shared" si="56"/>
         <v>-20.893800000000002</v>
       </c>
-      <c r="R35" s="69">
+      <c r="R35" s="68">
         <f t="shared" si="56"/>
         <v>-21.024000000000001</v>
       </c>
-      <c r="S35" s="69">
+      <c r="S35" s="68">
         <f>-S34*R32</f>
         <v>-22.0077</v>
       </c>
-      <c r="T35" s="73">
+      <c r="T35" s="72">
         <f>-T34*S32</f>
         <v>-22.982399999999998</v>
       </c>
-      <c r="AG35" s="27"/>
+      <c r="AG35" s="26"/>
     </row>
     <row r="36" spans="2:42" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="27"/>
-      <c r="C36" s="68" t="s">
+      <c r="B36" s="26"/>
+      <c r="C36" s="67" t="s">
         <v>151</v>
       </c>
-      <c r="E36" s="70">
+      <c r="E36" s="69">
         <f t="shared" ref="E36:R36" si="57">E32-D32-E35</f>
         <v>38.882800000000003</v>
       </c>
-      <c r="F36" s="70">
+      <c r="F36" s="69">
         <f t="shared" si="57"/>
         <v>38.743299999999998</v>
       </c>
-      <c r="G36" s="70">
+      <c r="G36" s="69">
         <f t="shared" si="57"/>
         <v>43.085799999999999</v>
       </c>
-      <c r="H36" s="70">
+      <c r="H36" s="69">
         <f t="shared" si="57"/>
         <v>42.088700000000003</v>
       </c>
-      <c r="I36" s="70">
+      <c r="I36" s="69">
         <f t="shared" si="57"/>
         <v>40.081199999999995</v>
       </c>
-      <c r="J36" s="70">
+      <c r="J36" s="69">
         <f t="shared" si="57"/>
         <v>34.668800000000005</v>
       </c>
-      <c r="K36" s="70">
+      <c r="K36" s="69">
         <f t="shared" si="57"/>
         <v>38.566000000000003</v>
       </c>
-      <c r="L36" s="70">
+      <c r="L36" s="69">
         <f t="shared" si="57"/>
         <v>39.445999999999998</v>
       </c>
-      <c r="M36" s="70">
+      <c r="M36" s="69">
         <f t="shared" si="57"/>
         <v>38.189499999999995</v>
       </c>
-      <c r="N36" s="70">
+      <c r="N36" s="69">
         <f t="shared" si="57"/>
         <v>33.341999999999999</v>
       </c>
-      <c r="O36" s="70">
+      <c r="O36" s="69">
         <f t="shared" si="57"/>
         <v>38.372700000000002</v>
       </c>
-      <c r="P36" s="70">
+      <c r="P36" s="69">
         <f t="shared" si="57"/>
         <v>34.965199999999996</v>
       </c>
-      <c r="Q36" s="70">
+      <c r="Q36" s="69">
         <f t="shared" si="57"/>
         <v>32.893799999999999</v>
       </c>
-      <c r="R36" s="70">
+      <c r="R36" s="69">
         <f t="shared" si="57"/>
         <v>32.024000000000001</v>
       </c>
-      <c r="S36" s="70">
+      <c r="S36" s="69">
         <f>S32-R32-S35</f>
         <v>37.0077</v>
       </c>
-      <c r="T36" s="74">
+      <c r="T36" s="73">
         <f>T32-S32-T35</f>
         <v>36.982399999999998</v>
       </c>
-      <c r="AG36" s="27"/>
+      <c r="AG36" s="26"/>
     </row>
     <row r="37" spans="2:42" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="27"/>
-      <c r="C37" s="71" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="H37" s="72">
+      <c r="H37" s="71">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="I37" s="72">
+      <c r="I37" s="71">
         <v>1.84E-2</v>
       </c>
-      <c r="J37" s="72">
+      <c r="J37" s="71">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="K37" s="72">
+      <c r="K37" s="71">
         <v>2.07E-2</v>
       </c>
-      <c r="L37" s="72">
+      <c r="L37" s="71">
         <v>2.1299999999999999E-2</v>
       </c>
-      <c r="M37" s="72">
+      <c r="M37" s="71">
         <v>2.3099999999999999E-2</v>
       </c>
-      <c r="N37" s="72">
+      <c r="N37" s="71">
         <v>2.3699999999999999E-2</v>
       </c>
-      <c r="O37" s="72">
+      <c r="O37" s="71">
         <v>2.58E-2</v>
       </c>
-      <c r="P37" s="72">
+      <c r="P37" s="71">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="Q37" s="72">
+      <c r="Q37" s="71">
         <v>2.6800000000000001E-2</v>
       </c>
-      <c r="R37" s="72">
+      <c r="R37" s="71">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="S37" s="72">
+      <c r="S37" s="71">
         <v>2.7400000000000001E-2</v>
       </c>
-      <c r="T37" s="75">
+      <c r="T37" s="74">
         <v>2.64E-2</v>
       </c>
-      <c r="AG37" s="27"/>
+      <c r="AG37" s="26"/>
     </row>
     <row r="38" spans="2:42" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="27"/>
+      <c r="B38" s="26"/>
       <c r="T38" s="3"/>
       <c r="U38" s="2"/>
       <c r="V38" s="2"/>
@@ -6741,7 +6796,7 @@
       <c r="AP38" s="2"/>
     </row>
     <row r="39" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="22"/>
+      <c r="B39" s="21"/>
       <c r="C39" s="1" t="s">
         <v>126</v>
       </c>
@@ -6793,10 +6848,10 @@
       <c r="S39" s="1">
         <v>603</v>
       </c>
-      <c r="T39" s="22">
+      <c r="T39" s="21">
         <v>602</v>
       </c>
-      <c r="AG39" s="22"/>
+      <c r="AG39" s="21"/>
     </row>
     <row r="40" spans="2:42" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
@@ -6946,7 +7001,7 @@
       <c r="S42" s="13"/>
       <c r="AE42" s="13"/>
       <c r="AF42" s="13"/>
-      <c r="AG42" s="27"/>
+      <c r="AG42" s="26"/>
       <c r="AH42" s="13"/>
       <c r="AI42" s="13"/>
       <c r="AJ42" s="13"/>
@@ -6977,7 +7032,7 @@
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
       <c r="S43" s="13"/>
-      <c r="T43" s="27"/>
+      <c r="T43" s="26"/>
       <c r="U43" s="13"/>
       <c r="V43" s="13"/>
       <c r="W43" s="13"/>
@@ -7552,7 +7607,7 @@
       </c>
     </row>
     <row r="51" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="22"/>
+      <c r="B51" s="21"/>
       <c r="C51" s="2" t="s">
         <v>73</v>
       </c>
@@ -7643,7 +7698,7 @@
       <c r="AP51" s="2"/>
     </row>
     <row r="52" spans="2:42" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="29"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="2" t="s">
         <v>74</v>
       </c>
@@ -7722,7 +7777,7 @@
       <c r="AF52" s="15">
         <v>600</v>
       </c>
-      <c r="AG52" s="22"/>
+      <c r="AG52" s="21"/>
       <c r="AH52" s="1"/>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
@@ -7801,7 +7856,7 @@
         <f t="shared" si="59"/>
         <v>7945</v>
       </c>
-      <c r="T53" s="28">
+      <c r="T53" s="27">
         <f t="shared" si="59"/>
         <v>8438</v>
       </c>
@@ -7835,7 +7890,7 @@
         <f t="shared" si="60"/>
         <v>7945</v>
       </c>
-      <c r="AG53" s="29"/>
+      <c r="AG53" s="28"/>
       <c r="AH53" s="6"/>
       <c r="AI53" s="6"/>
       <c r="AJ53" s="6"/>
@@ -7898,7 +7953,7 @@
       <c r="S54" s="17">
         <v>2436</v>
       </c>
-      <c r="T54" s="76">
+      <c r="T54" s="75">
         <v>2606</v>
       </c>
       <c r="U54" s="17"/>
@@ -8567,7 +8622,7 @@
       </c>
     </row>
     <row r="63" spans="2:42" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="29"/>
+      <c r="B63" s="28"/>
       <c r="C63" s="2" t="s">
         <v>85</v>
       </c>
@@ -8658,7 +8713,7 @@
       <c r="AP63" s="2"/>
     </row>
     <row r="64" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="22"/>
+      <c r="B64" s="21"/>
       <c r="C64" s="2" t="s">
         <v>86</v>
       </c>
@@ -8737,7 +8792,7 @@
       <c r="AF64" s="15">
         <v>809</v>
       </c>
-      <c r="AG64" s="29"/>
+      <c r="AG64" s="28"/>
       <c r="AH64" s="6"/>
       <c r="AI64" s="6"/>
       <c r="AJ64" s="6"/>
@@ -8816,7 +8871,7 @@
         <f t="shared" si="61"/>
         <v>5511</v>
       </c>
-      <c r="T65" s="76">
+      <c r="T65" s="75">
         <f t="shared" ref="T65" si="62">SUM(T55:T64)</f>
         <v>5833</v>
       </c>
@@ -8850,7 +8905,7 @@
         <f t="shared" si="63"/>
         <v>5509</v>
       </c>
-      <c r="AG65" s="22"/>
+      <c r="AG65" s="21"/>
       <c r="AH65" s="1"/>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
@@ -8929,7 +8984,7 @@
         <f t="shared" si="65"/>
         <v>7947</v>
       </c>
-      <c r="T66" s="28">
+      <c r="T66" s="27">
         <f t="shared" ref="T66" si="66">T54+T65</f>
         <v>8439</v>
       </c>
@@ -9373,7 +9428,7 @@
       </c>
     </row>
     <row r="73" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="22"/>
+      <c r="B73" s="21"/>
       <c r="C73" s="2" t="s">
         <v>94</v>
       </c>
@@ -9542,7 +9597,7 @@
       <c r="AF74" s="15">
         <v>-8</v>
       </c>
-      <c r="AG74" s="22"/>
+      <c r="AG74" s="21"/>
       <c r="AH74" s="1"/>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
@@ -9621,7 +9676,7 @@
         <f t="shared" si="75"/>
         <v>310</v>
       </c>
-      <c r="T75" s="28">
+      <c r="T75" s="27">
         <f t="shared" si="75"/>
         <v>373</v>
       </c>
@@ -9673,7 +9728,7 @@
       <c r="Q76" s="15"/>
       <c r="R76" s="15"/>
       <c r="S76" s="15"/>
-      <c r="T76" s="28"/>
+      <c r="T76" s="27"/>
       <c r="U76" s="16"/>
       <c r="V76" s="16"/>
       <c r="W76" s="16"/>
@@ -9688,7 +9743,7 @@
       <c r="AF76" s="15"/>
     </row>
     <row r="77" spans="2:42" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="22"/>
+      <c r="B77" s="21"/>
       <c r="C77" s="2" t="s">
         <v>97</v>
       </c>
@@ -9857,7 +9912,7 @@
       <c r="AF78" s="15">
         <v>-1</v>
       </c>
-      <c r="AG78" s="22"/>
+      <c r="AG78" s="21"/>
       <c r="AH78" s="1"/>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
@@ -9936,7 +9991,7 @@
         <f>SUM(S77:S78)</f>
         <v>-74</v>
       </c>
-      <c r="T79" s="28">
+      <c r="T79" s="27">
         <f>SUM(T77:T78)</f>
         <v>-78</v>
       </c>
@@ -9988,7 +10043,7 @@
       <c r="Q80" s="15"/>
       <c r="R80" s="15"/>
       <c r="S80" s="15"/>
-      <c r="T80" s="28"/>
+      <c r="T80" s="27"/>
       <c r="U80" s="16"/>
       <c r="V80" s="16"/>
       <c r="W80" s="16"/>
@@ -10413,7 +10468,7 @@
       <c r="AF85" s="15">
         <v>-261</v>
       </c>
-      <c r="AG85" s="22"/>
+      <c r="AG85" s="21"/>
       <c r="AH85" s="1"/>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
@@ -10492,7 +10547,7 @@
         <f>SUM(S81:S85)</f>
         <v>-183</v>
       </c>
-      <c r="T86" s="28">
+      <c r="T86" s="27">
         <f>SUM(T81:T85)</f>
         <v>-204</v>
       </c>
@@ -10968,7 +11023,7 @@
       <c r="Q94" s="16"/>
       <c r="R94" s="16"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="28"/>
+      <c r="T94" s="27"/>
       <c r="U94" s="16"/>
       <c r="V94" s="16"/>
       <c r="W94" s="16"/>
@@ -10981,7 +11036,7 @@
       <c r="AD94" s="16"/>
       <c r="AE94" s="16"/>
       <c r="AF94" s="16"/>
-      <c r="AG94" s="22"/>
+      <c r="AG94" s="21"/>
       <c r="AH94" s="1"/>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
@@ -11052,7 +11107,7 @@
       <c r="AC96" s="15"/>
       <c r="AD96" s="15"/>
       <c r="AE96" s="15"/>
-      <c r="AF96" s="43"/>
+      <c r="AF96" s="42"/>
     </row>
     <row r="97" spans="3:32" x14ac:dyDescent="0.25">
       <c r="D97" s="15"/>
@@ -11152,7 +11207,7 @@
       <c r="Q109" s="6"/>
       <c r="R109" s="6"/>
       <c r="S109" s="6"/>
-      <c r="T109" s="29"/>
+      <c r="T109" s="28"/>
       <c r="U109" s="6"/>
       <c r="V109" s="6"/>
       <c r="W109" s="6"/>
@@ -11252,7 +11307,7 @@
       <c r="F4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="50">
         <v>2022</v>
       </c>
       <c r="H4" s="4" t="s">
@@ -11267,7 +11322,7 @@
       <c r="K4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="51">
+      <c r="L4" s="50">
         <v>2023</v>
       </c>
       <c r="M4" s="4" t="s">
@@ -11282,7 +11337,7 @@
       <c r="P4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="51">
+      <c r="Q4" s="50">
         <v>2024</v>
       </c>
       <c r="R4" s="4" t="s">
@@ -11297,7 +11352,7 @@
       <c r="U4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="V4" s="51">
+      <c r="V4" s="50">
         <v>2025</v>
       </c>
       <c r="W4" s="4" t="s">
@@ -11312,7 +11367,7 @@
       <c r="Z4" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="AA4" s="47">
+      <c r="AA4" s="46">
         <v>2026</v>
       </c>
     </row>
@@ -11320,14 +11375,14 @@
       <c r="B5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G5" s="48"/>
+      <c r="G5" s="47"/>
       <c r="H5" s="1"/>
-      <c r="L5" s="48"/>
+      <c r="L5" s="47"/>
       <c r="N5" s="1"/>
-      <c r="Q5" s="48"/>
+      <c r="Q5" s="47"/>
       <c r="T5" s="1"/>
-      <c r="V5" s="48"/>
-      <c r="AA5" s="48"/>
+      <c r="V5" s="47"/>
+      <c r="AA5" s="47"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B6" s="15" t="s">
@@ -11345,7 +11400,7 @@
       <c r="F6" s="15">
         <v>396</v>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="51">
         <f>SUM(C6:F6)</f>
         <v>1374</v>
       </c>
@@ -11361,7 +11416,7 @@
       <c r="K6" s="15">
         <v>435</v>
       </c>
-      <c r="L6" s="52">
+      <c r="L6" s="51">
         <f>SUM(H6:K6)</f>
         <v>1586</v>
       </c>
@@ -11377,7 +11432,7 @@
       <c r="P6" s="15">
         <v>484</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="51">
         <f>SUM(M6:P6)</f>
         <v>1799</v>
       </c>
@@ -11393,14 +11448,14 @@
       <c r="U6" s="2">
         <v>556</v>
       </c>
-      <c r="V6" s="52">
+      <c r="V6" s="51">
         <f>SUM(R6:U6)</f>
         <v>2057</v>
       </c>
       <c r="W6" s="2">
         <v>532</v>
       </c>
-      <c r="AA6" s="52">
+      <c r="AA6" s="51">
         <f>SUM(W6:Z6)</f>
         <v>532</v>
       </c>
@@ -11410,7 +11465,7 @@
       <c r="B7" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="49"/>
+      <c r="G7" s="48"/>
       <c r="H7" s="19">
         <f t="shared" ref="H7:T7" si="0">(H6-C6)/C6</f>
         <v>0.26845637583892618</v>
@@ -11427,7 +11482,7 @@
         <f t="shared" si="0"/>
         <v>9.8484848484848481E-2</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="48">
         <f t="shared" si="0"/>
         <v>0.15429403202328967</v>
       </c>
@@ -11447,7 +11502,7 @@
         <f t="shared" si="0"/>
         <v>0.11264367816091954</v>
       </c>
-      <c r="Q7" s="49">
+      <c r="Q7" s="48">
         <f t="shared" si="0"/>
         <v>0.1343001261034048</v>
       </c>
@@ -11467,7 +11522,7 @@
         <f>(U6-P6)/P6</f>
         <v>0.1487603305785124</v>
       </c>
-      <c r="V7" s="49">
+      <c r="V7" s="48">
         <f t="shared" ref="V7:AA7" si="1">(V6-Q6)/Q6</f>
         <v>0.14341300722623679</v>
       </c>
@@ -11487,7 +11542,7 @@
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AA7" s="49">
+      <c r="AA7" s="48">
         <f t="shared" si="1"/>
         <v>-0.74137092853670394</v>
       </c>
@@ -11508,7 +11563,7 @@
       <c r="F8" s="15">
         <v>286</v>
       </c>
-      <c r="G8" s="52">
+      <c r="G8" s="51">
         <f>SUM(C8:F8)</f>
         <v>1160</v>
       </c>
@@ -11524,7 +11579,7 @@
       <c r="K8" s="15">
         <v>304</v>
       </c>
-      <c r="L8" s="52">
+      <c r="L8" s="51">
         <f>SUM(H8:K8)</f>
         <v>1250</v>
       </c>
@@ -11540,7 +11595,7 @@
       <c r="P8" s="15">
         <v>323</v>
       </c>
-      <c r="Q8" s="52">
+      <c r="Q8" s="51">
         <f>SUM(M8:P8)</f>
         <v>1293</v>
       </c>
@@ -11556,14 +11611,14 @@
       <c r="U8" s="2">
         <v>349</v>
       </c>
-      <c r="V8" s="52">
+      <c r="V8" s="51">
         <f>SUM(R8:U8)</f>
         <v>1410</v>
       </c>
       <c r="W8" s="2">
         <v>340</v>
       </c>
-      <c r="AA8" s="52">
+      <c r="AA8" s="51">
         <f>SUM(W8:Z8)</f>
         <v>340</v>
       </c>
@@ -11572,7 +11627,7 @@
       <c r="B9" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G9" s="49"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="19">
         <f t="shared" ref="H9:T9" si="2">(H8-C8)/C8</f>
         <v>0.11026615969581749</v>
@@ -11589,7 +11644,7 @@
         <f t="shared" si="2"/>
         <v>6.2937062937062943E-2</v>
       </c>
-      <c r="L9" s="49">
+      <c r="L9" s="48">
         <f t="shared" si="2"/>
         <v>7.7586206896551727E-2</v>
       </c>
@@ -11609,7 +11664,7 @@
         <f t="shared" si="2"/>
         <v>6.25E-2</v>
       </c>
-      <c r="Q9" s="49">
+      <c r="Q9" s="48">
         <f t="shared" si="2"/>
         <v>3.44E-2</v>
       </c>
@@ -11629,7 +11684,7 @@
         <f>(U8-P8)/P8</f>
         <v>8.0495356037151702E-2</v>
       </c>
-      <c r="V9" s="49">
+      <c r="V9" s="48">
         <f t="shared" ref="V9:AA9" si="3">(V8-Q8)/Q8</f>
         <v>9.0487238979118326E-2</v>
       </c>
@@ -11649,7 +11704,7 @@
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
-      <c r="AA9" s="49">
+      <c r="AA9" s="48">
         <f t="shared" si="3"/>
         <v>-0.75886524822695034</v>
       </c>
@@ -11674,7 +11729,7 @@
         <f>F6+F8</f>
         <v>682</v>
       </c>
-      <c r="G10" s="66">
+      <c r="G10" s="65">
         <f t="shared" ref="G10" si="5">G6+G8</f>
         <v>2534</v>
       </c>
@@ -11694,7 +11749,7 @@
         <f t="shared" si="6"/>
         <v>739</v>
       </c>
-      <c r="L10" s="66">
+      <c r="L10" s="65">
         <f t="shared" si="6"/>
         <v>2836</v>
       </c>
@@ -11714,7 +11769,7 @@
         <f>P6+P8</f>
         <v>807</v>
       </c>
-      <c r="Q10" s="66">
+      <c r="Q10" s="65">
         <f t="shared" ref="Q10" si="7">Q6+Q8</f>
         <v>3092</v>
       </c>
@@ -11734,7 +11789,7 @@
         <f>U6+U8</f>
         <v>905</v>
       </c>
-      <c r="V10" s="66">
+      <c r="V10" s="65">
         <f t="shared" ref="V10:Z10" si="8">V6+V8</f>
         <v>3467</v>
       </c>
@@ -11754,7 +11809,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AA10" s="66">
+      <c r="AA10" s="65">
         <f t="shared" ref="AA10" si="9">AA6+AA8</f>
         <v>872</v>
       </c>
@@ -11763,7 +11818,7 @@
       <c r="B11" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G11" s="49"/>
+      <c r="G11" s="48"/>
       <c r="H11" s="19">
         <f t="shared" ref="H11:T11" si="10">(H10-C10)/C10</f>
         <v>0.19429590017825313</v>
@@ -11780,7 +11835,7 @@
         <f t="shared" si="10"/>
         <v>8.357771260997067E-2</v>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="48">
         <f t="shared" si="10"/>
         <v>0.11917916337805841</v>
       </c>
@@ -11800,7 +11855,7 @@
         <f t="shared" si="10"/>
         <v>9.2016238159675232E-2</v>
       </c>
-      <c r="Q11" s="49">
+      <c r="Q11" s="48">
         <f t="shared" si="10"/>
         <v>9.0267983074753172E-2</v>
       </c>
@@ -11820,7 +11875,7 @@
         <f>(U10-P10)/P10</f>
         <v>0.12143742255266418</v>
       </c>
-      <c r="V11" s="67">
+      <c r="V11" s="66">
         <f t="shared" ref="V11:AA11" si="11">(V10-Q10)/Q10</f>
         <v>0.12128072445019406</v>
       </c>
@@ -11840,7 +11895,7 @@
         <f t="shared" si="11"/>
         <v>-1</v>
       </c>
-      <c r="AA11" s="49">
+      <c r="AA11" s="48">
         <f t="shared" si="11"/>
         <v>-0.74848572252668011</v>
       </c>
@@ -11861,8 +11916,8 @@
       <c r="F12" s="19">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G12" s="49"/>
-      <c r="H12" s="26">
+      <c r="G12" s="48"/>
+      <c r="H12" s="25">
         <v>0.19400000000000001</v>
       </c>
       <c r="I12" s="19">
@@ -11874,7 +11929,7 @@
       <c r="K12" s="19">
         <v>7.8E-2</v>
       </c>
-      <c r="L12" s="49">
+      <c r="L12" s="48">
         <v>0.115</v>
       </c>
       <c r="M12" s="19">
@@ -11889,7 +11944,7 @@
       <c r="P12" s="19">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="Q12" s="49">
+      <c r="Q12" s="48">
         <v>8.3000000000000004E-2</v>
       </c>
       <c r="R12" s="19">
@@ -11904,20 +11959,20 @@
       <c r="U12" s="19">
         <v>0.112</v>
       </c>
-      <c r="V12" s="49">
+      <c r="V12" s="48">
         <v>0.114</v>
       </c>
       <c r="W12" s="19">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AA12" s="49"/>
+      <c r="AA12" s="48"/>
     </row>
     <row r="13" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="G13" s="49"/>
+      <c r="G13" s="48"/>
       <c r="H13" s="19">
         <v>0.16200000000000001</v>
       </c>
@@ -11930,7 +11985,7 @@
       <c r="K13" s="19">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="L13" s="49"/>
+      <c r="L13" s="48"/>
       <c r="M13" s="19">
         <v>8.6999999999999994E-2</v>
       </c>
@@ -11943,7 +11998,7 @@
       <c r="P13" s="19">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="Q13" s="49"/>
+      <c r="Q13" s="48"/>
       <c r="R13" s="19">
         <v>5.8000000000000003E-2</v>
       </c>
@@ -11956,13 +12011,13 @@
       <c r="U13" s="19">
         <v>9.4E-2</v>
       </c>
-      <c r="V13" s="49">
+      <c r="V13" s="48">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="W13" s="19">
         <v>4.7E-2</v>
       </c>
-      <c r="AA13" s="49"/>
+      <c r="AA13" s="48"/>
     </row>
     <row r="14" spans="1:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
@@ -11980,7 +12035,7 @@
       <c r="F14" s="15">
         <v>550</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="65">
         <f>SUM(C14:F14)</f>
         <v>1977</v>
       </c>
@@ -11996,7 +12051,7 @@
       <c r="K14" s="15">
         <v>580</v>
       </c>
-      <c r="L14" s="66">
+      <c r="L14" s="65">
         <f>SUM(H14:K14)</f>
         <v>2193</v>
       </c>
@@ -12012,7 +12067,7 @@
       <c r="P14" s="15">
         <v>628</v>
       </c>
-      <c r="Q14" s="66">
+      <c r="Q14" s="65">
         <f>SUM(M14:P14)</f>
         <v>2363</v>
       </c>
@@ -12028,14 +12083,14 @@
       <c r="U14" s="15">
         <v>709</v>
       </c>
-      <c r="V14" s="66">
+      <c r="V14" s="65">
         <f>SUM(R14:U14)</f>
         <v>2632</v>
       </c>
       <c r="W14" s="15">
         <v>679</v>
       </c>
-      <c r="AA14" s="66">
+      <c r="AA14" s="65">
         <f>SUM(W14:Z14)</f>
         <v>679</v>
       </c>
@@ -12056,11 +12111,11 @@
       <c r="F15" s="19">
         <v>0.80300000000000005</v>
       </c>
-      <c r="G15" s="67">
+      <c r="G15" s="66">
         <f>G14/G10</f>
         <v>0.78018942383583267</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="25">
         <v>0.78</v>
       </c>
       <c r="I15" s="19">
@@ -12072,7 +12127,7 @@
       <c r="K15" s="19">
         <v>0.78200000000000003</v>
       </c>
-      <c r="L15" s="67">
+      <c r="L15" s="66">
         <f>L14/L10</f>
         <v>0.77327221438645977</v>
       </c>
@@ -12088,7 +12143,7 @@
       <c r="P15" s="19">
         <v>0.77500000000000002</v>
       </c>
-      <c r="Q15" s="67">
+      <c r="Q15" s="66">
         <f>Q14/Q10</f>
         <v>0.76423027166882274</v>
       </c>
@@ -12104,14 +12159,14 @@
       <c r="U15" s="19">
         <v>0.78</v>
       </c>
-      <c r="V15" s="67">
+      <c r="V15" s="66">
         <f>V14/V10</f>
         <v>0.75915777329102974</v>
       </c>
       <c r="W15" s="19">
         <v>0.77500000000000002</v>
       </c>
-      <c r="AA15" s="67">
+      <c r="AA15" s="66">
         <f>AA14/AA10</f>
         <v>0.77866972477064222</v>
       </c>
@@ -12132,7 +12187,7 @@
       <c r="F16" s="15">
         <v>213</v>
       </c>
-      <c r="G16" s="66">
+      <c r="G16" s="65">
         <f>SUM(C16:F16)</f>
         <v>758</v>
       </c>
@@ -12148,7 +12203,7 @@
       <c r="K16" s="15">
         <v>252</v>
       </c>
-      <c r="L16" s="66">
+      <c r="L16" s="65">
         <f>SUM(H16:K16)</f>
         <v>895</v>
       </c>
@@ -12164,7 +12219,7 @@
       <c r="P16" s="15">
         <v>259</v>
       </c>
-      <c r="Q16" s="66">
+      <c r="Q16" s="65">
         <f>SUM(M16:P16)</f>
         <v>979</v>
       </c>
@@ -12180,18 +12235,18 @@
       <c r="U16" s="15">
         <v>286</v>
       </c>
-      <c r="V16" s="66">
+      <c r="V16" s="65">
         <f>SUM(R16:U16)</f>
         <v>1060</v>
       </c>
       <c r="W16" s="15">
         <v>267</v>
       </c>
-      <c r="AA16" s="66">
+      <c r="AA16" s="65">
         <f>SUM(W16:Z16)</f>
         <v>267</v>
       </c>
-      <c r="AC16" s="42"/>
+      <c r="AC16" s="41"/>
     </row>
     <row r="17" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="19" t="s">
@@ -12209,7 +12264,7 @@
       <c r="F17" s="19">
         <v>0.312</v>
       </c>
-      <c r="G17" s="67">
+      <c r="G17" s="66">
         <f>G16/G10</f>
         <v>0.29913180741910023</v>
       </c>
@@ -12225,7 +12280,7 @@
       <c r="K17" s="19">
         <v>0.34100000000000003</v>
       </c>
-      <c r="L17" s="67">
+      <c r="L17" s="66">
         <f>L16/L10</f>
         <v>0.31558533145275036</v>
       </c>
@@ -12241,7 +12296,7 @@
       <c r="P17" s="19">
         <v>0.32</v>
       </c>
-      <c r="Q17" s="67">
+      <c r="Q17" s="66">
         <f>Q16/Q10</f>
         <v>0.3166235446313066</v>
       </c>
@@ -12257,14 +12312,14 @@
       <c r="U17" s="19">
         <v>0.315</v>
       </c>
-      <c r="V17" s="67">
+      <c r="V17" s="66">
         <f>V16/V10</f>
         <v>0.30573983270839344</v>
       </c>
       <c r="W17" s="19">
         <v>0.30499999999999999</v>
       </c>
-      <c r="AA17" s="67">
+      <c r="AA17" s="66">
         <f>AA16/AA10</f>
         <v>0.30619266055045874</v>
       </c>
@@ -12273,11 +12328,11 @@
       <c r="B18" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="66">
+      <c r="G18" s="65">
         <f>SUM(C18:F18)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="66">
+      <c r="L18" s="65">
         <f>SUM(H18:K18)</f>
         <v>0</v>
       </c>
@@ -12293,7 +12348,7 @@
       <c r="P18" s="15">
         <v>189</v>
       </c>
-      <c r="Q18" s="66">
+      <c r="Q18" s="65">
         <f>SUM(M18:P18)</f>
         <v>710</v>
       </c>
@@ -12309,29 +12364,29 @@
       <c r="U18" s="15">
         <v>206</v>
       </c>
-      <c r="V18" s="66">
+      <c r="V18" s="65">
         <f>SUM(R18:U18)</f>
         <v>760</v>
       </c>
       <c r="W18" s="15">
         <v>185</v>
       </c>
-      <c r="AA18" s="66">
+      <c r="AA18" s="65">
         <f>SUM(W18:Z18)</f>
         <v>185</v>
       </c>
-      <c r="AC18" s="43"/>
+      <c r="AC18" s="42"/>
     </row>
     <row r="19" spans="1:29" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="67">
+      <c r="G19" s="66">
         <f>G18/G10</f>
         <v>0</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="L19" s="67">
+      <c r="H19" s="25"/>
+      <c r="L19" s="66">
         <f>L18/L10</f>
         <v>0</v>
       </c>
@@ -12349,7 +12404,7 @@
       <c r="P19" s="19">
         <v>0.23400000000000001</v>
       </c>
-      <c r="Q19" s="67">
+      <c r="Q19" s="66">
         <f>Q18/Q10</f>
         <v>0.22962483829236741</v>
       </c>
@@ -12366,93 +12421,93 @@
       <c r="U19" s="19">
         <v>0.22700000000000001</v>
       </c>
-      <c r="V19" s="67">
+      <c r="V19" s="66">
         <f>V18/V10</f>
         <v>0.21920969137582924</v>
       </c>
       <c r="W19" s="19">
         <v>0.21199999999999999</v>
       </c>
-      <c r="AA19" s="67">
+      <c r="AA19" s="66">
         <f>AA18/AA10</f>
         <v>0.2121559633027523</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="44" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" s="43" customFormat="1" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="45">
+      <c r="C20" s="44">
         <v>231</v>
       </c>
-      <c r="D20" s="45">
+      <c r="D20" s="44">
         <v>238</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="44">
         <v>238</v>
       </c>
-      <c r="F20" s="45">
+      <c r="F20" s="44">
         <v>246</v>
       </c>
-      <c r="G20" s="53"/>
-      <c r="H20" s="46">
+      <c r="G20" s="52"/>
+      <c r="H20" s="45">
         <v>245</v>
       </c>
-      <c r="I20" s="45">
+      <c r="I20" s="44">
         <v>244</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="44">
         <v>246</v>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="44">
         <v>250</v>
       </c>
-      <c r="L20" s="53"/>
-      <c r="M20" s="45">
+      <c r="L20" s="52"/>
+      <c r="M20" s="44">
         <v>251</v>
       </c>
-      <c r="N20" s="45">
+      <c r="N20" s="44">
         <v>257</v>
       </c>
-      <c r="O20" s="45">
+      <c r="O20" s="44">
         <v>258</v>
       </c>
-      <c r="P20" s="45">
+      <c r="P20" s="44">
         <v>262</v>
       </c>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="45">
+      <c r="Q20" s="52"/>
+      <c r="R20" s="44">
         <v>263</v>
       </c>
-      <c r="S20" s="45">
+      <c r="S20" s="44">
         <v>268</v>
       </c>
-      <c r="T20" s="45">
+      <c r="T20" s="44">
         <v>269</v>
       </c>
-      <c r="U20" s="44">
+      <c r="U20" s="43">
         <v>270</v>
       </c>
-      <c r="V20" s="50"/>
-      <c r="W20" s="44">
+      <c r="V20" s="49"/>
+      <c r="W20" s="43">
         <v>269</v>
       </c>
-      <c r="AA20" s="50"/>
-      <c r="AC20" s="45"/>
+      <c r="AA20" s="49"/>
+      <c r="AC20" s="44"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="48"/>
+      <c r="G21" s="47"/>
       <c r="H21" s="1"/>
-      <c r="L21" s="48"/>
+      <c r="L21" s="47"/>
       <c r="N21" s="1"/>
-      <c r="Q21" s="48"/>
+      <c r="Q21" s="47"/>
       <c r="T21" s="1"/>
-      <c r="V21" s="48"/>
-      <c r="AA21" s="48"/>
+      <c r="V21" s="47"/>
+      <c r="AA21" s="47"/>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
@@ -12470,7 +12525,7 @@
       <c r="F22" s="15">
         <v>126</v>
       </c>
-      <c r="G22" s="52">
+      <c r="G22" s="51">
         <f>SUM(C22:F22)</f>
         <v>494</v>
       </c>
@@ -12486,7 +12541,7 @@
       <c r="K22" s="15">
         <v>123</v>
       </c>
-      <c r="L22" s="52">
+      <c r="L22" s="51">
         <f>SUM(H22:K22)</f>
         <v>558</v>
       </c>
@@ -12502,7 +12557,7 @@
       <c r="P22" s="15">
         <v>133</v>
       </c>
-      <c r="Q22" s="52">
+      <c r="Q22" s="51">
         <f>SUM(M22:P22)</f>
         <v>557</v>
       </c>
@@ -12518,14 +12573,14 @@
       <c r="U22" s="2">
         <v>105</v>
       </c>
-      <c r="V22" s="52">
+      <c r="V22" s="51">
         <f>SUM(R22:U22)</f>
         <v>465</v>
       </c>
       <c r="W22" s="2">
         <v>132</v>
       </c>
-      <c r="AA22" s="52">
+      <c r="AA22" s="51">
         <f>SUM(W22:Z22)</f>
         <v>132</v>
       </c>
@@ -12538,7 +12593,7 @@
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
-      <c r="G23" s="49"/>
+      <c r="G23" s="48"/>
       <c r="H23" s="19">
         <f t="shared" ref="H23" si="12">(H22-C22)/C22</f>
         <v>0.28813559322033899</v>
@@ -12555,7 +12610,7 @@
         <f t="shared" ref="K23:L23" si="14">(K22-F22)/F22</f>
         <v>-2.3809523809523808E-2</v>
       </c>
-      <c r="L23" s="49">
+      <c r="L23" s="48">
         <f t="shared" si="14"/>
         <v>0.12955465587044535</v>
       </c>
@@ -12575,7 +12630,7 @@
         <f t="shared" ref="P23:Q23" si="18">(P22-K22)/K22</f>
         <v>8.1300813008130079E-2</v>
       </c>
-      <c r="Q23" s="49">
+      <c r="Q23" s="48">
         <f t="shared" si="18"/>
         <v>-1.7921146953405018E-3</v>
       </c>
@@ -12595,7 +12650,7 @@
         <f>(U22-P22)/P22</f>
         <v>-0.21052631578947367</v>
       </c>
-      <c r="V23" s="49">
+      <c r="V23" s="48">
         <f t="shared" ref="V23" si="22">(V22-Q22)/Q22</f>
         <v>-0.16517055655296231</v>
       </c>
@@ -12615,7 +12670,7 @@
         <f t="shared" ref="Z23:AA23" si="26">(Z22-U22)/U22</f>
         <v>-1</v>
       </c>
-      <c r="AA23" s="49">
+      <c r="AA23" s="48">
         <f t="shared" si="26"/>
         <v>-0.71612903225806457</v>
       </c>
@@ -12636,7 +12691,7 @@
       <c r="F24" s="15">
         <v>140</v>
       </c>
-      <c r="G24" s="52">
+      <c r="G24" s="51">
         <f>SUM(C24:F24)</f>
         <v>597</v>
       </c>
@@ -12652,7 +12707,7 @@
       <c r="K24" s="15">
         <v>154</v>
       </c>
-      <c r="L24" s="52">
+      <c r="L24" s="51">
         <f>SUM(H24:K24)</f>
         <v>622</v>
       </c>
@@ -12668,7 +12723,7 @@
       <c r="P24" s="15">
         <v>155</v>
       </c>
-      <c r="Q24" s="52">
+      <c r="Q24" s="51">
         <f>SUM(M24:P24)</f>
         <v>643</v>
       </c>
@@ -12684,14 +12739,14 @@
       <c r="U24" s="2">
         <v>162</v>
       </c>
-      <c r="V24" s="52">
+      <c r="V24" s="51">
         <f>SUM(R24:U24)</f>
         <v>678</v>
       </c>
       <c r="W24" s="2">
         <v>153</v>
       </c>
-      <c r="AA24" s="52">
+      <c r="AA24" s="51">
         <f>SUM(W24:Z24)</f>
         <v>153</v>
       </c>
@@ -12704,7 +12759,7 @@
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
-      <c r="G25" s="49"/>
+      <c r="G25" s="48"/>
       <c r="H25" s="19">
         <f t="shared" ref="H25" si="27">(H24-C24)/C24</f>
         <v>5.0359712230215826E-2</v>
@@ -12721,7 +12776,7 @@
         <f t="shared" ref="K25:L25" si="29">(K24-F24)/F24</f>
         <v>0.1</v>
       </c>
-      <c r="L25" s="49">
+      <c r="L25" s="48">
         <f t="shared" si="29"/>
         <v>4.1876046901172533E-2</v>
       </c>
@@ -12741,7 +12796,7 @@
         <f t="shared" ref="P25:Q25" si="33">(P24-K24)/K24</f>
         <v>6.4935064935064939E-3</v>
       </c>
-      <c r="Q25" s="49">
+      <c r="Q25" s="48">
         <f t="shared" si="33"/>
         <v>3.3762057877813507E-2</v>
       </c>
@@ -12761,7 +12816,7 @@
         <f>(U24-P24)/P24</f>
         <v>4.5161290322580643E-2</v>
       </c>
-      <c r="V25" s="49">
+      <c r="V25" s="48">
         <f t="shared" ref="V25" si="37">(V24-Q24)/Q24</f>
         <v>5.4432348367029551E-2</v>
       </c>
@@ -12781,7 +12836,7 @@
         <f t="shared" ref="Z25:AA25" si="41">(Z24-U24)/U24</f>
         <v>-1</v>
       </c>
-      <c r="AA25" s="49">
+      <c r="AA25" s="48">
         <f t="shared" si="41"/>
         <v>-0.77433628318584069</v>
       </c>
@@ -12806,7 +12861,7 @@
         <f>F22+F24</f>
         <v>266</v>
       </c>
-      <c r="G26" s="66">
+      <c r="G26" s="65">
         <f t="shared" ref="G26" si="43">G22+G24</f>
         <v>1091</v>
       </c>
@@ -12826,7 +12881,7 @@
         <f t="shared" si="44"/>
         <v>277</v>
       </c>
-      <c r="L26" s="66">
+      <c r="L26" s="65">
         <f t="shared" si="44"/>
         <v>1180</v>
       </c>
@@ -12846,7 +12901,7 @@
         <f>P22+P24</f>
         <v>288</v>
       </c>
-      <c r="Q26" s="66">
+      <c r="Q26" s="65">
         <f t="shared" ref="Q26" si="45">Q22+Q24</f>
         <v>1200</v>
       </c>
@@ -12866,7 +12921,7 @@
         <f>U22+U24</f>
         <v>267</v>
       </c>
-      <c r="V26" s="66">
+      <c r="V26" s="65">
         <f t="shared" ref="V26" si="47">V22+V24</f>
         <v>1143</v>
       </c>
@@ -12886,7 +12941,7 @@
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="AA26" s="66">
+      <c r="AA26" s="65">
         <f t="shared" si="48"/>
         <v>285</v>
       </c>
@@ -12899,7 +12954,7 @@
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
-      <c r="G27" s="49"/>
+      <c r="G27" s="48"/>
       <c r="H27" s="19">
         <f t="shared" ref="H27" si="49">(H26-C26)/C26</f>
         <v>0.15953307392996108</v>
@@ -12916,7 +12971,7 @@
         <f t="shared" ref="K27:L27" si="51">(K26-F26)/F26</f>
         <v>4.1353383458646614E-2</v>
       </c>
-      <c r="L27" s="49">
+      <c r="L27" s="48">
         <f t="shared" si="51"/>
         <v>8.1576535288725938E-2</v>
       </c>
@@ -12936,7 +12991,7 @@
         <f t="shared" ref="P27:Q27" si="55">(P26-K26)/K26</f>
         <v>3.9711191335740074E-2</v>
       </c>
-      <c r="Q27" s="49">
+      <c r="Q27" s="48">
         <f t="shared" si="55"/>
         <v>1.6949152542372881E-2</v>
       </c>
@@ -12956,7 +13011,7 @@
         <f>(U26-P26)/P26</f>
         <v>-7.2916666666666671E-2</v>
       </c>
-      <c r="V27" s="49">
+      <c r="V27" s="48">
         <f t="shared" ref="V27" si="59">(V26-Q26)/Q26</f>
         <v>-4.7500000000000001E-2</v>
       </c>
@@ -12976,7 +13031,7 @@
         <f t="shared" ref="Z27:AA27" si="63">(Z26-U26)/U26</f>
         <v>-1</v>
       </c>
-      <c r="AA27" s="49">
+      <c r="AA27" s="48">
         <f t="shared" si="63"/>
         <v>-0.75065616797900259</v>
       </c>
@@ -12997,8 +13052,8 @@
       <c r="F28" s="19">
         <v>-5.2999999999999999E-2</v>
       </c>
-      <c r="G28" s="49"/>
-      <c r="H28" s="26">
+      <c r="G28" s="48"/>
+      <c r="H28" s="25">
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="I28" s="19">
@@ -13010,7 +13065,7 @@
       <c r="K28" s="19">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="L28" s="49">
+      <c r="L28" s="48">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="M28" s="19">
@@ -13025,7 +13080,7 @@
       <c r="P28" s="19">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q28" s="49">
+      <c r="Q28" s="48">
         <v>0.02</v>
       </c>
       <c r="R28" s="19">
@@ -13040,7 +13095,7 @@
       <c r="U28" s="19">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="V28" s="49">
+      <c r="V28" s="48">
         <v>-1.4E-2</v>
       </c>
       <c r="W28" s="19">
@@ -13049,7 +13104,7 @@
       <c r="X28" s="19"/>
       <c r="Y28" s="19"/>
       <c r="Z28" s="19"/>
-      <c r="AA28" s="49"/>
+      <c r="AA28" s="48"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
@@ -13059,7 +13114,7 @@
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
-      <c r="G29" s="49"/>
+      <c r="G29" s="48"/>
       <c r="H29" s="19">
         <v>8.3000000000000004E-2</v>
       </c>
@@ -13072,7 +13127,7 @@
       <c r="K29" s="19">
         <v>-4.0000000000000001E-3</v>
       </c>
-      <c r="L29" s="49"/>
+      <c r="L29" s="48"/>
       <c r="M29" s="19">
         <v>-2.5999999999999999E-2</v>
       </c>
@@ -13085,7 +13140,7 @@
       <c r="P29" s="19">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q29" s="49"/>
+      <c r="Q29" s="48"/>
       <c r="R29" s="19">
         <v>-3.6999999999999998E-2</v>
       </c>
@@ -13098,7 +13153,7 @@
       <c r="U29" s="19">
         <v>-3.4000000000000002E-2</v>
       </c>
-      <c r="V29" s="49">
+      <c r="V29" s="48">
         <v>-3.4000000000000002E-2</v>
       </c>
       <c r="W29" s="19">
@@ -13107,7 +13162,7 @@
       <c r="X29" s="19"/>
       <c r="Y29" s="19"/>
       <c r="Z29" s="19"/>
-      <c r="AA29" s="49"/>
+      <c r="AA29" s="48"/>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
@@ -13125,7 +13180,7 @@
       <c r="F30" s="2">
         <v>204</v>
       </c>
-      <c r="G30" s="66">
+      <c r="G30" s="65">
         <f>SUM(C30:F30)</f>
         <v>836</v>
       </c>
@@ -13141,7 +13196,7 @@
       <c r="K30" s="2">
         <v>209</v>
       </c>
-      <c r="L30" s="66">
+      <c r="L30" s="65">
         <f>SUM(H30:K30)</f>
         <v>893</v>
       </c>
@@ -13157,7 +13212,7 @@
       <c r="P30" s="2">
         <v>220</v>
       </c>
-      <c r="Q30" s="66">
+      <c r="Q30" s="65">
         <f>SUM(M30:P30)</f>
         <v>908</v>
       </c>
@@ -13173,14 +13228,14 @@
       <c r="U30" s="2">
         <v>204</v>
       </c>
-      <c r="V30" s="66">
+      <c r="V30" s="65">
         <f>SUM(R30:U30)</f>
         <v>860</v>
       </c>
       <c r="W30" s="2">
         <v>202</v>
       </c>
-      <c r="AA30" s="66">
+      <c r="AA30" s="65">
         <f>SUM(W30:Z30)</f>
         <v>202</v>
       </c>
@@ -13201,11 +13256,11 @@
       <c r="F31" s="19">
         <v>0.76300000000000001</v>
       </c>
-      <c r="G31" s="67">
+      <c r="G31" s="66">
         <f>G30/G26</f>
         <v>0.76626947754353802</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="25">
         <v>0.77300000000000002</v>
       </c>
       <c r="I31" s="19">
@@ -13217,7 +13272,7 @@
       <c r="K31" s="19">
         <v>0.751</v>
       </c>
-      <c r="L31" s="67">
+      <c r="L31" s="66">
         <f>L30/L26</f>
         <v>0.75677966101694916</v>
       </c>
@@ -13233,7 +13288,7 @@
       <c r="P31" s="19">
         <v>0.76600000000000001</v>
       </c>
-      <c r="Q31" s="67">
+      <c r="Q31" s="66">
         <f>Q30/Q26</f>
         <v>0.75666666666666671</v>
       </c>
@@ -13249,7 +13304,7 @@
       <c r="U31" s="19">
         <v>0.752</v>
       </c>
-      <c r="V31" s="67">
+      <c r="V31" s="66">
         <f>V30/V26</f>
         <v>0.75240594925634297</v>
       </c>
@@ -13259,7 +13314,7 @@
       <c r="X31" s="19"/>
       <c r="Y31" s="19"/>
       <c r="Z31" s="19"/>
-      <c r="AA31" s="67">
+      <c r="AA31" s="66">
         <f>AA30/AA26</f>
         <v>0.70877192982456139</v>
       </c>
@@ -13280,7 +13335,7 @@
       <c r="F32" s="2">
         <v>58</v>
       </c>
-      <c r="G32" s="66">
+      <c r="G32" s="65">
         <f>SUM(C32:F32)</f>
         <v>277</v>
       </c>
@@ -13296,7 +13351,7 @@
       <c r="K32" s="2">
         <v>51</v>
       </c>
-      <c r="L32" s="66">
+      <c r="L32" s="65">
         <f>SUM(H32:K32)</f>
         <v>280</v>
       </c>
@@ -13312,7 +13367,7 @@
       <c r="P32" s="2">
         <v>61</v>
       </c>
-      <c r="Q32" s="66">
+      <c r="Q32" s="65">
         <f>SUM(M32:P32)</f>
         <v>294</v>
       </c>
@@ -13328,19 +13383,19 @@
       <c r="U32" s="2">
         <v>48</v>
       </c>
-      <c r="V32" s="66">
+      <c r="V32" s="65">
         <f>SUM(R32:U32)</f>
         <v>235</v>
       </c>
       <c r="W32" s="2">
         <v>45</v>
       </c>
-      <c r="AA32" s="66">
+      <c r="AA32" s="65">
         <f>SUM(W32:Z32)</f>
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B33" s="19" t="s">
         <v>38</v>
       </c>
@@ -13356,7 +13411,7 @@
       <c r="F33" s="19">
         <v>0.218</v>
       </c>
-      <c r="G33" s="67">
+      <c r="G33" s="66">
         <f>G32/G26</f>
         <v>0.25389550870760769</v>
       </c>
@@ -13372,7 +13427,7 @@
       <c r="K33" s="19">
         <v>0.183</v>
       </c>
-      <c r="L33" s="67">
+      <c r="L33" s="66">
         <f>L32/L26</f>
         <v>0.23728813559322035</v>
       </c>
@@ -13388,7 +13443,7 @@
       <c r="P33" s="19">
         <v>0.21299999999999999</v>
       </c>
-      <c r="Q33" s="67">
+      <c r="Q33" s="66">
         <f>Q32/Q26</f>
         <v>0.245</v>
       </c>
@@ -13404,7 +13459,7 @@
       <c r="U33" s="19">
         <v>0.17899999999999999</v>
       </c>
-      <c r="V33" s="67">
+      <c r="V33" s="66">
         <f>V32/V26</f>
         <v>0.20559930008748906</v>
       </c>
@@ -13414,20 +13469,20 @@
       <c r="X33" s="19"/>
       <c r="Y33" s="19"/>
       <c r="Z33" s="19"/>
-      <c r="AA33" s="67">
+      <c r="AA33" s="66">
         <f>AA32/AA26</f>
         <v>0.15789473684210525</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G34" s="66">
+      <c r="G34" s="65">
         <f>SUM(C34:F34)</f>
         <v>0</v>
       </c>
-      <c r="L34" s="66">
+      <c r="L34" s="65">
         <f>SUM(H34:K34)</f>
         <v>0</v>
       </c>
@@ -13443,7 +13498,7 @@
       <c r="P34" s="2">
         <v>33</v>
       </c>
-      <c r="Q34" s="66">
+      <c r="Q34" s="65">
         <f>SUM(M34:P34)</f>
         <v>190</v>
       </c>
@@ -13459,19 +13514,20 @@
       <c r="U34" s="2">
         <v>20</v>
       </c>
-      <c r="V34" s="66">
+      <c r="V34" s="65">
         <f>SUM(R34:U34)</f>
         <v>121</v>
       </c>
       <c r="W34" s="2">
         <v>17</v>
       </c>
-      <c r="AA34" s="66">
+      <c r="AA34" s="65">
         <f>SUM(W34:Z34)</f>
         <v>17</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AC34" s="42"/>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B35" s="19" t="s">
         <v>34</v>
       </c>
@@ -13479,15 +13535,15 @@
       <c r="D35" s="19"/>
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
-      <c r="G35" s="67">
+      <c r="G35" s="66">
         <f>G34/G26</f>
         <v>0</v>
       </c>
-      <c r="H35" s="26"/>
+      <c r="H35" s="25"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
-      <c r="L35" s="67">
+      <c r="L35" s="66">
         <f>L34/L26</f>
         <v>0</v>
       </c>
@@ -13505,7 +13561,7 @@
       <c r="P35" s="19">
         <v>0.115</v>
       </c>
-      <c r="Q35" s="67">
+      <c r="Q35" s="66">
         <f>Q34/Q26</f>
         <v>0.15833333333333333</v>
       </c>
@@ -13522,7 +13578,7 @@
       <c r="U35" s="19">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="V35" s="67">
+      <c r="V35" s="66">
         <f>V34/V26</f>
         <v>0.10586176727909011</v>
       </c>
@@ -13532,89 +13588,89 @@
       <c r="X35" s="19"/>
       <c r="Y35" s="19"/>
       <c r="Z35" s="19"/>
-      <c r="AA35" s="67">
+      <c r="AA35" s="66">
         <f>AA34/AA26</f>
         <v>5.9649122807017542E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:27" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="44" t="s">
+    <row r="36" spans="2:29" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="45">
+      <c r="C36" s="44">
         <v>116</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="44">
         <v>116</v>
       </c>
-      <c r="E36" s="45">
+      <c r="E36" s="44">
         <v>116</v>
       </c>
-      <c r="F36" s="45">
+      <c r="F36" s="44">
         <v>116</v>
       </c>
-      <c r="G36" s="53"/>
-      <c r="H36" s="46">
+      <c r="G36" s="52"/>
+      <c r="H36" s="45">
         <v>116</v>
       </c>
-      <c r="I36" s="45">
+      <c r="I36" s="44">
         <v>116</v>
       </c>
-      <c r="J36" s="45">
+      <c r="J36" s="44">
         <v>115</v>
       </c>
-      <c r="K36" s="45">
+      <c r="K36" s="44">
         <v>114</v>
       </c>
-      <c r="L36" s="53"/>
-      <c r="M36" s="45">
+      <c r="L36" s="52"/>
+      <c r="M36" s="44">
         <v>114</v>
       </c>
-      <c r="N36" s="45">
+      <c r="N36" s="44">
         <v>114</v>
       </c>
-      <c r="O36" s="45">
+      <c r="O36" s="44">
         <v>115</v>
       </c>
-      <c r="P36" s="45">
+      <c r="P36" s="44">
         <v>115</v>
       </c>
-      <c r="Q36" s="53"/>
-      <c r="R36" s="45">
+      <c r="Q36" s="52"/>
+      <c r="R36" s="44">
         <v>116</v>
       </c>
-      <c r="S36" s="45">
+      <c r="S36" s="44">
         <v>117</v>
       </c>
-      <c r="T36" s="45">
+      <c r="T36" s="44">
         <v>117</v>
       </c>
-      <c r="U36" s="44">
+      <c r="U36" s="43">
         <v>115</v>
       </c>
-      <c r="V36" s="50"/>
-      <c r="W36" s="44">
+      <c r="V36" s="49"/>
+      <c r="W36" s="43">
         <v>114</v>
       </c>
-      <c r="X36" s="44"/>
-      <c r="Y36" s="44"/>
-      <c r="Z36" s="44"/>
-      <c r="AA36" s="50"/>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="X36" s="43"/>
+      <c r="Y36" s="43"/>
+      <c r="Z36" s="43"/>
+      <c r="AA36" s="49"/>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="G37" s="48"/>
+      <c r="G37" s="47"/>
       <c r="H37" s="1"/>
-      <c r="L37" s="48"/>
+      <c r="L37" s="47"/>
       <c r="N37" s="1"/>
-      <c r="Q37" s="48"/>
+      <c r="Q37" s="47"/>
       <c r="T37" s="1"/>
-      <c r="V37" s="48"/>
-      <c r="AA37" s="48"/>
-    </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="V37" s="47"/>
+      <c r="AA37" s="47"/>
+    </row>
+    <row r="38" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>133</v>
       </c>
@@ -13630,7 +13686,7 @@
       <c r="F38" s="15">
         <v>143</v>
       </c>
-      <c r="G38" s="52">
+      <c r="G38" s="51">
         <f>SUM(C38:F38)</f>
         <v>506</v>
       </c>
@@ -13646,7 +13702,7 @@
       <c r="K38" s="15">
         <v>139</v>
       </c>
-      <c r="L38" s="52">
+      <c r="L38" s="51">
         <f>SUM(H38:K38)</f>
         <v>546</v>
       </c>
@@ -13662,7 +13718,7 @@
       <c r="P38" s="15">
         <v>166</v>
       </c>
-      <c r="Q38" s="52">
+      <c r="Q38" s="51">
         <f>SUM(M38:P38)</f>
         <v>620</v>
       </c>
@@ -13678,16 +13734,16 @@
       <c r="U38" s="2">
         <v>177</v>
       </c>
-      <c r="V38" s="52">
+      <c r="V38" s="51">
         <f>SUM(R38:U38)</f>
         <v>687</v>
       </c>
       <c r="W38" s="2">
         <v>177</v>
       </c>
-      <c r="AA38" s="48"/>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA38" s="47"/>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B39" s="19" t="s">
         <v>134</v>
       </c>
@@ -13695,7 +13751,7 @@
       <c r="D39" s="19"/>
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
-      <c r="G39" s="49"/>
+      <c r="G39" s="48"/>
       <c r="H39" s="19">
         <f t="shared" ref="H39" si="64">(H38-C38)/C38</f>
         <v>0.21621621621621623</v>
@@ -13712,7 +13768,7 @@
         <f t="shared" ref="K39:L39" si="66">(K38-F38)/F38</f>
         <v>-2.7972027972027972E-2</v>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="48">
         <f t="shared" si="66"/>
         <v>7.9051383399209488E-2</v>
       </c>
@@ -13732,7 +13788,7 @@
         <f t="shared" ref="P39:Q39" si="70">(P38-K38)/K38</f>
         <v>0.19424460431654678</v>
       </c>
-      <c r="Q39" s="49">
+      <c r="Q39" s="48">
         <f t="shared" si="70"/>
         <v>0.13553113553113552</v>
       </c>
@@ -13752,7 +13808,7 @@
         <f>(U38-P38)/P38</f>
         <v>6.6265060240963861E-2</v>
       </c>
-      <c r="V39" s="49">
+      <c r="V39" s="48">
         <f>(V38-Q38)/Q38</f>
         <v>0.10806451612903226</v>
       </c>
@@ -13772,12 +13828,12 @@
         <f t="shared" ref="Z39" si="77">(Z38-U38)/U38</f>
         <v>-1</v>
       </c>
-      <c r="AA39" s="49">
+      <c r="AA39" s="48">
         <f t="shared" ref="AA39" si="78">(AA38-V38)/V38</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>135</v>
       </c>
@@ -13793,7 +13849,7 @@
       <c r="F40" s="15">
         <v>141</v>
       </c>
-      <c r="G40" s="52">
+      <c r="G40" s="51">
         <f>SUM(C40:F40)</f>
         <v>622</v>
       </c>
@@ -13809,7 +13865,7 @@
       <c r="K40" s="15">
         <v>137</v>
       </c>
-      <c r="L40" s="52">
+      <c r="L40" s="51">
         <f>SUM(H40:K40)</f>
         <v>629</v>
       </c>
@@ -13825,7 +13881,7 @@
       <c r="P40" s="15">
         <v>149</v>
       </c>
-      <c r="Q40" s="52">
+      <c r="Q40" s="51">
         <f>SUM(M40:P40)</f>
         <v>639</v>
       </c>
@@ -13841,16 +13897,16 @@
       <c r="U40" s="2">
         <v>148</v>
       </c>
-      <c r="V40" s="52">
+      <c r="V40" s="51">
         <f>SUM(R40:U40)</f>
         <v>678</v>
       </c>
       <c r="W40" s="2">
         <v>166</v>
       </c>
-      <c r="AA40" s="48"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA40" s="47"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B41" s="19" t="s">
         <v>134</v>
       </c>
@@ -13858,7 +13914,7 @@
       <c r="D41" s="19"/>
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
-      <c r="G41" s="49"/>
+      <c r="G41" s="48"/>
       <c r="H41" s="19">
         <f t="shared" ref="H41" si="79">(H40-C40)/C40</f>
         <v>2.0547945205479451E-2</v>
@@ -13875,7 +13931,7 @@
         <f t="shared" ref="K41" si="81">(K40-F40)/F40</f>
         <v>-2.8368794326241134E-2</v>
       </c>
-      <c r="L41" s="49">
+      <c r="L41" s="48">
         <f t="shared" ref="L41" si="82">(L40-G40)/G40</f>
         <v>1.1254019292604502E-2</v>
       </c>
@@ -13895,7 +13951,7 @@
         <f t="shared" ref="P41:Q41" si="86">(P40-K40)/K40</f>
         <v>8.7591240875912413E-2</v>
       </c>
-      <c r="Q41" s="49">
+      <c r="Q41" s="48">
         <f t="shared" si="86"/>
         <v>1.5898251192368838E-2</v>
       </c>
@@ -13915,7 +13971,7 @@
         <f>(U40-P40)/P40</f>
         <v>-6.7114093959731542E-3</v>
       </c>
-      <c r="V41" s="49">
+      <c r="V41" s="48">
         <f t="shared" ref="V41" si="90">(V40-Q40)/Q40</f>
         <v>6.1032863849765258E-2</v>
       </c>
@@ -13935,12 +13991,12 @@
         <f t="shared" ref="Z41" si="94">(Z40-U40)/U40</f>
         <v>-1</v>
       </c>
-      <c r="AA41" s="49">
+      <c r="AA41" s="48">
         <f t="shared" ref="AA41" si="95">(AA40-V40)/V40</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="2:27" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:29" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
         <v>136</v>
       </c>
@@ -13960,7 +14016,7 @@
         <f>F38+F40</f>
         <v>284</v>
       </c>
-      <c r="G42" s="66">
+      <c r="G42" s="65">
         <f t="shared" ref="G42:O42" si="97">G38+G40</f>
         <v>1128</v>
       </c>
@@ -13980,7 +14036,7 @@
         <f t="shared" si="97"/>
         <v>276</v>
       </c>
-      <c r="L42" s="66">
+      <c r="L42" s="65">
         <f t="shared" si="97"/>
         <v>1175</v>
       </c>
@@ -14000,7 +14056,7 @@
         <f>P38+P40</f>
         <v>315</v>
       </c>
-      <c r="Q42" s="66">
+      <c r="Q42" s="65">
         <f t="shared" ref="Q42:T42" si="98">Q38+Q40</f>
         <v>1259</v>
       </c>
@@ -14020,7 +14076,7 @@
         <f>U38+U40</f>
         <v>325</v>
       </c>
-      <c r="V42" s="66">
+      <c r="V42" s="65">
         <f t="shared" ref="V42:AA42" si="99">V38+V40</f>
         <v>1365</v>
       </c>
@@ -14040,12 +14096,12 @@
         <f t="shared" si="99"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="66">
+      <c r="AA42" s="65">
         <f t="shared" si="99"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B43" s="19" t="s">
         <v>134</v>
       </c>
@@ -14053,7 +14109,7 @@
       <c r="D43" s="19"/>
       <c r="E43" s="19"/>
       <c r="F43" s="19"/>
-      <c r="G43" s="49"/>
+      <c r="G43" s="48"/>
       <c r="H43" s="19">
         <f t="shared" ref="H43" si="100">(H42-C42)/C42</f>
         <v>0.10505836575875487</v>
@@ -14070,7 +14126,7 @@
         <f t="shared" ref="K43" si="102">(K42-F42)/F42</f>
         <v>-2.8169014084507043E-2</v>
       </c>
-      <c r="L43" s="49">
+      <c r="L43" s="48">
         <f t="shared" ref="L43" si="103">(L42-G42)/G42</f>
         <v>4.1666666666666664E-2</v>
       </c>
@@ -14090,7 +14146,7 @@
         <f t="shared" ref="P43" si="107">(P42-K42)/K42</f>
         <v>0.14130434782608695</v>
       </c>
-      <c r="Q43" s="49">
+      <c r="Q43" s="48">
         <f t="shared" ref="Q43" si="108">(Q42-L42)/L42</f>
         <v>7.1489361702127663E-2</v>
       </c>
@@ -14110,7 +14166,7 @@
         <f>(U42-P42)/P42</f>
         <v>3.1746031746031744E-2</v>
       </c>
-      <c r="V43" s="49">
+      <c r="V43" s="48">
         <f t="shared" ref="V43" si="112">(V42-Q42)/Q42</f>
         <v>8.4193804606830819E-2</v>
       </c>
@@ -14130,12 +14186,12 @@
         <f t="shared" ref="Z43" si="116">(Z42-U42)/U42</f>
         <v>-1</v>
       </c>
-      <c r="AA43" s="49">
+      <c r="AA43" s="48">
         <f t="shared" ref="AA43" si="117">(AA42-V42)/V42</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B44" s="19" t="s">
         <v>109</v>
       </c>
@@ -14151,8 +14207,8 @@
       <c r="F44" s="19">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="G44" s="49"/>
-      <c r="H44" s="26">
+      <c r="G44" s="48"/>
+      <c r="H44" s="25">
         <v>0.14099999999999999</v>
       </c>
       <c r="I44" s="19">
@@ -14164,7 +14220,7 @@
       <c r="K44" s="19">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="L44" s="49">
+      <c r="L44" s="48">
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="M44" s="19">
@@ -14179,7 +14235,7 @@
       <c r="P44" s="19">
         <v>0.14599999999999999</v>
       </c>
-      <c r="Q44" s="49">
+      <c r="Q44" s="48">
         <v>9.6000000000000002E-2</v>
       </c>
       <c r="R44" s="19">
@@ -14194,7 +14250,7 @@
       <c r="U44" s="19">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="V44" s="49">
+      <c r="V44" s="48">
         <v>0.13100000000000001</v>
       </c>
       <c r="W44" s="19">
@@ -14203,9 +14259,9 @@
       <c r="X44" s="19"/>
       <c r="Y44" s="19"/>
       <c r="Z44" s="19"/>
-      <c r="AA44" s="49"/>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA44" s="48"/>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B45" s="19" t="s">
         <v>111</v>
       </c>
@@ -14213,7 +14269,7 @@
       <c r="D45" s="19"/>
       <c r="E45" s="19"/>
       <c r="F45" s="19"/>
-      <c r="G45" s="49"/>
+      <c r="G45" s="48"/>
       <c r="H45" s="19">
         <v>0.104</v>
       </c>
@@ -14226,7 +14282,7 @@
       <c r="K45" s="19">
         <v>1.2E-2</v>
       </c>
-      <c r="L45" s="49"/>
+      <c r="L45" s="48"/>
       <c r="M45" s="19">
         <v>2.3E-2</v>
       </c>
@@ -14239,7 +14295,7 @@
       <c r="P45" s="19">
         <v>9.4E-2</v>
       </c>
-      <c r="Q45" s="49"/>
+      <c r="Q45" s="48"/>
       <c r="R45" s="19">
         <v>0.152</v>
       </c>
@@ -14252,7 +14308,7 @@
       <c r="U45" s="19">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="V45" s="49">
+      <c r="V45" s="48">
         <v>0.09</v>
       </c>
       <c r="W45" s="19">
@@ -14261,9 +14317,9 @@
       <c r="X45" s="19"/>
       <c r="Y45" s="19"/>
       <c r="Z45" s="19"/>
-      <c r="AA45" s="49"/>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA45" s="48"/>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B46" s="2" t="s">
         <v>51</v>
       </c>
@@ -14279,7 +14335,7 @@
       <c r="F46" s="2">
         <v>224</v>
       </c>
-      <c r="G46" s="66">
+      <c r="G46" s="65">
         <f>SUM(C46:F46)</f>
         <v>848</v>
       </c>
@@ -14295,7 +14351,7 @@
       <c r="K46" s="2">
         <v>210</v>
       </c>
-      <c r="L46" s="66">
+      <c r="L46" s="65">
         <f>SUM(H46:K46)</f>
         <v>861</v>
       </c>
@@ -14311,7 +14367,7 @@
       <c r="P46" s="2">
         <v>235</v>
       </c>
-      <c r="Q46" s="66">
+      <c r="Q46" s="65">
         <f>SUM(M46:P46)</f>
         <v>912</v>
       </c>
@@ -14327,19 +14383,19 @@
       <c r="U46" s="2">
         <v>237</v>
       </c>
-      <c r="V46" s="66">
+      <c r="V46" s="65">
         <f>SUM(R46:U46)</f>
         <v>965</v>
       </c>
       <c r="W46" s="2">
         <v>249</v>
       </c>
-      <c r="AA46" s="66">
+      <c r="AA46" s="65">
         <f>SUM(W46:Z46)</f>
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B47" s="19" t="s">
         <v>36</v>
       </c>
@@ -14355,11 +14411,11 @@
       <c r="F47" s="19">
         <v>0.78400000000000003</v>
       </c>
-      <c r="G47" s="67">
+      <c r="G47" s="66">
         <f>G46/G42</f>
         <v>0.75177304964539005</v>
       </c>
-      <c r="H47" s="26">
+      <c r="H47" s="25">
         <v>0.75600000000000001</v>
       </c>
       <c r="I47" s="19">
@@ -14371,7 +14427,7 @@
       <c r="K47" s="19">
         <v>0.75800000000000001</v>
       </c>
-      <c r="L47" s="67">
+      <c r="L47" s="66">
         <f>L46/L42</f>
         <v>0.7327659574468085</v>
       </c>
@@ -14387,7 +14443,7 @@
       <c r="P47" s="19">
         <v>0.74399999999999999</v>
       </c>
-      <c r="Q47" s="67">
+      <c r="Q47" s="66">
         <f>Q46/Q42</f>
         <v>0.72438443208895953</v>
       </c>
@@ -14403,7 +14459,7 @@
       <c r="U47" s="19">
         <v>0.72299999999999998</v>
       </c>
-      <c r="V47" s="67">
+      <c r="V47" s="66">
         <f>V46/V42</f>
         <v>0.706959706959707</v>
       </c>
@@ -14413,12 +14469,12 @@
       <c r="X47" s="19"/>
       <c r="Y47" s="19"/>
       <c r="Z47" s="19"/>
-      <c r="AA47" s="67" t="e">
+      <c r="AA47" s="66" t="e">
         <f>AA46/AA42</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>54</v>
       </c>
@@ -14434,7 +14490,7 @@
       <c r="F48" s="2">
         <v>53</v>
       </c>
-      <c r="G48" s="66">
+      <c r="G48" s="65">
         <f>SUM(C48:F48)</f>
         <v>239</v>
       </c>
@@ -14450,7 +14506,7 @@
       <c r="K48" s="2">
         <v>48</v>
       </c>
-      <c r="L48" s="66">
+      <c r="L48" s="65">
         <f>SUM(H48:K48)</f>
         <v>237</v>
       </c>
@@ -14466,7 +14522,7 @@
       <c r="P48" s="2">
         <v>49</v>
       </c>
-      <c r="Q48" s="66">
+      <c r="Q48" s="65">
         <f>SUM(M48:P48)</f>
         <v>241</v>
       </c>
@@ -14482,19 +14538,19 @@
       <c r="U48" s="2">
         <v>59</v>
       </c>
-      <c r="V48" s="66">
+      <c r="V48" s="65">
         <f>SUM(R48:U48)</f>
         <v>274</v>
       </c>
       <c r="W48" s="2">
         <v>57</v>
       </c>
-      <c r="AA48" s="66">
+      <c r="AA48" s="65">
         <f>SUM(W48:Z48)</f>
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B49" s="19" t="s">
         <v>38</v>
       </c>
@@ -14510,7 +14566,7 @@
       <c r="F49" s="19">
         <v>0.185</v>
       </c>
-      <c r="G49" s="67">
+      <c r="G49" s="66">
         <f>G48/G42</f>
         <v>0.21187943262411346</v>
       </c>
@@ -14526,7 +14582,7 @@
       <c r="K49" s="19">
         <v>0.17399999999999999</v>
       </c>
-      <c r="L49" s="67">
+      <c r="L49" s="66">
         <f>L48/L42</f>
         <v>0.20170212765957446</v>
       </c>
@@ -14542,7 +14598,7 @@
       <c r="P49" s="19">
         <v>0.156</v>
       </c>
-      <c r="Q49" s="67">
+      <c r="Q49" s="66">
         <f>Q48/Q42</f>
         <v>0.19142176330420968</v>
       </c>
@@ -14558,7 +14614,7 @@
       <c r="U49" s="19">
         <v>0.18</v>
       </c>
-      <c r="V49" s="67">
+      <c r="V49" s="66">
         <f>V48/V42</f>
         <v>0.20073260073260074</v>
       </c>
@@ -14568,20 +14624,20 @@
       <c r="X49" s="19"/>
       <c r="Y49" s="19"/>
       <c r="Z49" s="19"/>
-      <c r="AA49" s="67" t="e">
+      <c r="AA49" s="66" t="e">
         <f>AA48/AA42</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="66">
+      <c r="G50" s="65">
         <f>SUM(C50:F50)</f>
         <v>0</v>
       </c>
-      <c r="L50" s="66">
+      <c r="L50" s="65">
         <f>SUM(H50:K50)</f>
         <v>0</v>
       </c>
@@ -14597,7 +14653,7 @@
       <c r="P50" s="2">
         <v>19</v>
       </c>
-      <c r="Q50" s="66">
+      <c r="Q50" s="65">
         <f>SUM(M50:P50)</f>
         <v>129</v>
       </c>
@@ -14613,19 +14669,20 @@
       <c r="U50" s="2">
         <v>29</v>
       </c>
-      <c r="V50" s="66">
+      <c r="V50" s="65">
         <f>SUM(R50:U50)</f>
         <v>155</v>
       </c>
       <c r="W50" s="2">
         <v>25</v>
       </c>
-      <c r="AA50" s="66">
+      <c r="AA50" s="65">
         <f>SUM(W50:Z50)</f>
         <v>25</v>
       </c>
-    </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AC50" s="42"/>
+    </row>
+    <row r="51" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B51" s="19" t="s">
         <v>34</v>
       </c>
@@ -14633,15 +14690,15 @@
       <c r="D51" s="19"/>
       <c r="E51" s="19"/>
       <c r="F51" s="19"/>
-      <c r="G51" s="67">
+      <c r="G51" s="66">
         <f>G50/G42</f>
         <v>0</v>
       </c>
-      <c r="H51" s="26"/>
+      <c r="H51" s="25"/>
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
-      <c r="L51" s="67">
+      <c r="L51" s="66">
         <f>L50/L42</f>
         <v>0</v>
       </c>
@@ -14659,7 +14716,7 @@
       <c r="P51" s="19">
         <v>6.2E-2</v>
       </c>
-      <c r="Q51" s="67">
+      <c r="Q51" s="66">
         <f>Q50/Q42</f>
         <v>0.10246227164416204</v>
       </c>
@@ -14676,7 +14733,7 @@
       <c r="U51" s="19">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="V51" s="67">
+      <c r="V51" s="66">
         <f>V50/V42</f>
         <v>0.11355311355311355</v>
       </c>
@@ -14686,89 +14743,89 @@
       <c r="X51" s="19"/>
       <c r="Y51" s="19"/>
       <c r="Z51" s="19"/>
-      <c r="AA51" s="67" t="e">
+      <c r="AA51" s="66" t="e">
         <f>AA50/AA42</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="52" spans="2:27" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="44" t="s">
+    <row r="52" spans="2:29" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C52" s="45">
+      <c r="C52" s="44">
         <v>112</v>
       </c>
-      <c r="D52" s="45">
+      <c r="D52" s="44">
         <v>114</v>
       </c>
-      <c r="E52" s="45">
+      <c r="E52" s="44">
         <v>113</v>
       </c>
-      <c r="F52" s="45">
+      <c r="F52" s="44">
         <v>116</v>
       </c>
-      <c r="G52" s="53"/>
-      <c r="H52" s="46">
+      <c r="G52" s="52"/>
+      <c r="H52" s="45">
         <v>118</v>
       </c>
-      <c r="I52" s="45">
+      <c r="I52" s="44">
         <v>118</v>
       </c>
-      <c r="J52" s="45">
+      <c r="J52" s="44">
         <v>119</v>
       </c>
-      <c r="K52" s="45">
+      <c r="K52" s="44">
         <v>120</v>
       </c>
-      <c r="L52" s="53"/>
-      <c r="M52" s="45">
+      <c r="L52" s="52"/>
+      <c r="M52" s="44">
         <v>121</v>
       </c>
-      <c r="N52" s="45">
+      <c r="N52" s="44">
         <v>122</v>
       </c>
-      <c r="O52" s="45">
+      <c r="O52" s="44">
         <v>127</v>
       </c>
-      <c r="P52" s="45">
+      <c r="P52" s="44">
         <v>131</v>
       </c>
-      <c r="Q52" s="53"/>
-      <c r="R52" s="45">
+      <c r="Q52" s="52"/>
+      <c r="R52" s="44">
         <v>132</v>
       </c>
-      <c r="S52" s="45">
+      <c r="S52" s="44">
         <v>132</v>
       </c>
-      <c r="T52" s="45">
+      <c r="T52" s="44">
         <v>134</v>
       </c>
-      <c r="U52" s="44">
+      <c r="U52" s="43">
         <v>136</v>
       </c>
-      <c r="V52" s="50"/>
-      <c r="W52" s="44">
+      <c r="V52" s="49"/>
+      <c r="W52" s="43">
         <v>136</v>
       </c>
-      <c r="X52" s="44"/>
-      <c r="Y52" s="44"/>
-      <c r="Z52" s="44"/>
-      <c r="AA52" s="50"/>
-    </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="X52" s="43"/>
+      <c r="Y52" s="43"/>
+      <c r="Z52" s="43"/>
+      <c r="AA52" s="49"/>
+    </row>
+    <row r="53" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="G53" s="48"/>
+      <c r="G53" s="47"/>
       <c r="H53" s="1"/>
-      <c r="L53" s="48"/>
+      <c r="L53" s="47"/>
       <c r="N53" s="1"/>
-      <c r="Q53" s="48"/>
+      <c r="Q53" s="47"/>
       <c r="T53" s="1"/>
-      <c r="V53" s="48"/>
-      <c r="AA53" s="48"/>
-    </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="V53" s="47"/>
+      <c r="AA53" s="47"/>
+    </row>
+    <row r="54" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>133</v>
       </c>
@@ -14784,7 +14841,7 @@
       <c r="F54" s="15">
         <v>55</v>
       </c>
-      <c r="G54" s="52">
+      <c r="G54" s="51">
         <f>SUM(C54:F54)</f>
         <v>187</v>
       </c>
@@ -14800,7 +14857,7 @@
       <c r="K54" s="15">
         <v>80</v>
       </c>
-      <c r="L54" s="52">
+      <c r="L54" s="51">
         <f>SUM(H54:K54)</f>
         <v>291</v>
       </c>
@@ -14816,7 +14873,7 @@
       <c r="P54" s="15">
         <v>99</v>
       </c>
-      <c r="Q54" s="52">
+      <c r="Q54" s="51">
         <f>SUM(M54:P54)</f>
         <v>354</v>
       </c>
@@ -14832,16 +14889,16 @@
       <c r="U54" s="2">
         <v>121</v>
       </c>
-      <c r="V54" s="52">
+      <c r="V54" s="51">
         <f>SUM(R54:U54)</f>
         <v>435</v>
       </c>
       <c r="W54" s="2">
         <v>116</v>
       </c>
-      <c r="AA54" s="48"/>
-    </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA54" s="47"/>
+    </row>
+    <row r="55" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B55" s="19" t="s">
         <v>134</v>
       </c>
@@ -14849,7 +14906,7 @@
       <c r="D55" s="19"/>
       <c r="E55" s="19"/>
       <c r="F55" s="19"/>
-      <c r="G55" s="49"/>
+      <c r="G55" s="48"/>
       <c r="H55" s="19">
         <f t="shared" ref="H55" si="118">(H54-C54)/C54</f>
         <v>0.67567567567567566</v>
@@ -14866,7 +14923,7 @@
         <f t="shared" ref="K55" si="120">(K54-F54)/F54</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="L55" s="49">
+      <c r="L55" s="48">
         <f>(L54-G54)/G54</f>
         <v>0.55614973262032086</v>
       </c>
@@ -14886,7 +14943,7 @@
         <f t="shared" ref="P55" si="124">(P54-K54)/K54</f>
         <v>0.23749999999999999</v>
       </c>
-      <c r="Q55" s="49">
+      <c r="Q55" s="48">
         <f>(Q54-L54)/L54</f>
         <v>0.21649484536082475</v>
       </c>
@@ -14906,7 +14963,7 @@
         <f>(U54-P54)/P54</f>
         <v>0.22222222222222221</v>
       </c>
-      <c r="V55" s="49">
+      <c r="V55" s="48">
         <f>(V54-Q54)/Q54</f>
         <v>0.2288135593220339</v>
       </c>
@@ -14926,12 +14983,12 @@
         <f t="shared" ref="Z55" si="131">(Z54-U54)/U54</f>
         <v>-1</v>
       </c>
-      <c r="AA55" s="49">
+      <c r="AA55" s="48">
         <f t="shared" ref="AA55" si="132">(AA54-V54)/V54</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>135</v>
       </c>
@@ -14947,7 +15004,7 @@
       <c r="F56" s="15">
         <v>52</v>
       </c>
-      <c r="G56" s="52">
+      <c r="G56" s="51">
         <f>SUM(C56:F56)</f>
         <v>206</v>
       </c>
@@ -14963,7 +15020,7 @@
       <c r="K56" s="15">
         <v>74</v>
       </c>
-      <c r="L56" s="52">
+      <c r="L56" s="51">
         <f>SUM(H56:K56)</f>
         <v>300</v>
       </c>
@@ -14979,7 +15036,7 @@
       <c r="P56" s="15">
         <v>82</v>
       </c>
-      <c r="Q56" s="52">
+      <c r="Q56" s="51">
         <f>SUM(M56:P56)</f>
         <v>356</v>
       </c>
@@ -14995,16 +15052,16 @@
       <c r="U56" s="2">
         <v>98</v>
       </c>
-      <c r="V56" s="52">
+      <c r="V56" s="51">
         <f>SUM(R56:U56)</f>
         <v>414</v>
       </c>
       <c r="W56" s="2">
         <v>102</v>
       </c>
-      <c r="AA56" s="48"/>
-    </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA56" s="47"/>
+    </row>
+    <row r="57" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B57" s="19" t="s">
         <v>134</v>
       </c>
@@ -15012,7 +15069,7 @@
       <c r="D57" s="19"/>
       <c r="E57" s="19"/>
       <c r="F57" s="19"/>
-      <c r="G57" s="49"/>
+      <c r="G57" s="48"/>
       <c r="H57" s="19">
         <f t="shared" ref="H57" si="133">(H56-C56)/C56</f>
         <v>0.45454545454545453</v>
@@ -15029,7 +15086,7 @@
         <f t="shared" ref="K57" si="135">(K56-F56)/F56</f>
         <v>0.42307692307692307</v>
       </c>
-      <c r="L57" s="49">
+      <c r="L57" s="48">
         <f t="shared" ref="L57" si="136">(L56-G56)/G56</f>
         <v>0.4563106796116505</v>
       </c>
@@ -15049,7 +15106,7 @@
         <f t="shared" ref="P57:Q57" si="140">(P56-K56)/K56</f>
         <v>0.10810810810810811</v>
       </c>
-      <c r="Q57" s="49">
+      <c r="Q57" s="48">
         <f t="shared" si="140"/>
         <v>0.18666666666666668</v>
       </c>
@@ -15069,7 +15126,7 @@
         <f>(U56-P56)/P56</f>
         <v>0.1951219512195122</v>
       </c>
-      <c r="V57" s="49">
+      <c r="V57" s="48">
         <f t="shared" ref="V57" si="144">(V56-Q56)/Q56</f>
         <v>0.16292134831460675</v>
       </c>
@@ -15089,12 +15146,12 @@
         <f t="shared" ref="Z57" si="148">(Z56-U56)/U56</f>
         <v>-1</v>
       </c>
-      <c r="AA57" s="49">
+      <c r="AA57" s="48">
         <f t="shared" ref="AA57" si="149">(AA56-V56)/V56</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>136</v>
       </c>
@@ -15114,7 +15171,7 @@
         <f>F54+F56</f>
         <v>107</v>
       </c>
-      <c r="G58" s="66">
+      <c r="G58" s="65">
         <f>G54+G56</f>
         <v>393</v>
       </c>
@@ -15134,7 +15191,7 @@
         <f t="shared" si="151"/>
         <v>154</v>
       </c>
-      <c r="L58" s="47">
+      <c r="L58" s="46">
         <f t="shared" si="151"/>
         <v>591</v>
       </c>
@@ -15154,7 +15211,7 @@
         <f>P54+P56</f>
         <v>181</v>
       </c>
-      <c r="Q58" s="47">
+      <c r="Q58" s="46">
         <f t="shared" ref="Q58:T58" si="152">Q54+Q56</f>
         <v>710</v>
       </c>
@@ -15174,7 +15231,7 @@
         <f>U54+U56</f>
         <v>219</v>
       </c>
-      <c r="V58" s="47">
+      <c r="V58" s="46">
         <f t="shared" ref="V58:AA58" si="153">V54+V56</f>
         <v>849</v>
       </c>
@@ -15194,12 +15251,12 @@
         <f t="shared" si="153"/>
         <v>0</v>
       </c>
-      <c r="AA58" s="47">
+      <c r="AA58" s="46">
         <f t="shared" si="153"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B59" s="19" t="s">
         <v>134</v>
       </c>
@@ -15207,7 +15264,7 @@
       <c r="D59" s="19"/>
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
-      <c r="G59" s="49"/>
+      <c r="G59" s="48"/>
       <c r="H59" s="19">
         <f t="shared" ref="H59" si="154">(H58-C58)/C58</f>
         <v>0.55555555555555558</v>
@@ -15224,7 +15281,7 @@
         <f t="shared" ref="K59" si="156">(K58-F58)/F58</f>
         <v>0.43925233644859812</v>
       </c>
-      <c r="L59" s="49">
+      <c r="L59" s="48">
         <f t="shared" ref="L59" si="157">(L58-G58)/G58</f>
         <v>0.50381679389312972</v>
       </c>
@@ -15244,7 +15301,7 @@
         <f t="shared" ref="P59" si="161">(P58-K58)/K58</f>
         <v>0.17532467532467533</v>
       </c>
-      <c r="Q59" s="49">
+      <c r="Q59" s="48">
         <f t="shared" ref="Q59" si="162">(Q58-L58)/L58</f>
         <v>0.20135363790186125</v>
       </c>
@@ -15264,7 +15321,7 @@
         <f>(U58-P58)/P58</f>
         <v>0.20994475138121546</v>
       </c>
-      <c r="V59" s="49">
+      <c r="V59" s="48">
         <f t="shared" ref="V59" si="166">(V58-Q58)/Q58</f>
         <v>0.19577464788732393</v>
       </c>
@@ -15284,12 +15341,12 @@
         <f t="shared" ref="Z59" si="170">(Z58-U58)/U58</f>
         <v>-1</v>
       </c>
-      <c r="AA59" s="49">
+      <c r="AA59" s="48">
         <f t="shared" ref="AA59" si="171">(AA58-V58)/V58</f>
         <v>-1</v>
       </c>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B60" s="19" t="s">
         <v>109</v>
       </c>
@@ -15305,8 +15362,8 @@
       <c r="F60" s="19">
         <v>0.32600000000000001</v>
       </c>
-      <c r="G60" s="49"/>
-      <c r="H60" s="26">
+      <c r="G60" s="48"/>
+      <c r="H60" s="25">
         <v>0.44500000000000001</v>
       </c>
       <c r="I60" s="19">
@@ -15318,7 +15375,7 @@
       <c r="K60" s="19">
         <v>0.35899999999999999</v>
       </c>
-      <c r="L60" s="49">
+      <c r="L60" s="48">
         <v>0.39100000000000001</v>
       </c>
       <c r="M60" s="19">
@@ -15333,7 +15390,7 @@
       <c r="P60" s="19">
         <v>0.17599999999999999</v>
       </c>
-      <c r="Q60" s="49">
+      <c r="Q60" s="48">
         <v>0.20799999999999999</v>
       </c>
       <c r="R60" s="19">
@@ -15348,7 +15405,7 @@
       <c r="U60" s="19">
         <v>0.27100000000000002</v>
       </c>
-      <c r="V60" s="49">
+      <c r="V60" s="48">
         <v>0.23799999999999999</v>
       </c>
       <c r="W60" s="19">
@@ -15357,9 +15414,9 @@
       <c r="X60" s="19"/>
       <c r="Y60" s="19"/>
       <c r="Z60" s="19"/>
-      <c r="AA60" s="49"/>
-    </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA60" s="48"/>
+    </row>
+    <row r="61" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B61" s="19" t="s">
         <v>111</v>
       </c>
@@ -15367,7 +15424,7 @@
       <c r="D61" s="19"/>
       <c r="E61" s="19"/>
       <c r="F61" s="19"/>
-      <c r="G61" s="49"/>
+      <c r="G61" s="48"/>
       <c r="H61" s="19">
         <v>0.28000000000000003</v>
       </c>
@@ -15380,7 +15437,7 @@
       <c r="K61" s="19">
         <v>0.189</v>
       </c>
-      <c r="L61" s="49"/>
+      <c r="L61" s="48"/>
       <c r="M61" s="19">
         <v>0.08</v>
       </c>
@@ -15393,7 +15450,7 @@
       <c r="P61" s="19">
         <v>6.2E-2</v>
       </c>
-      <c r="Q61" s="49"/>
+      <c r="Q61" s="48"/>
       <c r="R61" s="19">
         <v>0.16</v>
       </c>
@@ -15406,7 +15463,7 @@
       <c r="U61" s="19">
         <v>0.21199999999999999</v>
       </c>
-      <c r="V61" s="49">
+      <c r="V61" s="48">
         <v>0.156</v>
       </c>
       <c r="W61" s="19">
@@ -15415,9 +15472,10 @@
       <c r="X61" s="19"/>
       <c r="Y61" s="19"/>
       <c r="Z61" s="19"/>
-      <c r="AA61" s="49"/>
-    </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="AA61" s="48"/>
+      <c r="AC61" s="42"/>
+    </row>
+    <row r="62" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>51</v>
       </c>
@@ -15433,7 +15491,7 @@
       <c r="F62" s="2">
         <v>77</v>
       </c>
-      <c r="G62" s="66">
+      <c r="G62" s="65">
         <f>SUM(C62:F62)</f>
         <v>275</v>
       </c>
@@ -15449,7 +15507,7 @@
       <c r="K62" s="2">
         <v>108</v>
       </c>
-      <c r="L62" s="66">
+      <c r="L62" s="65">
         <f>SUM(H62:K62)</f>
         <v>407</v>
       </c>
@@ -15465,7 +15523,7 @@
       <c r="P62" s="2">
         <v>128</v>
       </c>
-      <c r="Q62" s="66">
+      <c r="Q62" s="65">
         <f>SUM(M62:P62)</f>
         <v>486</v>
       </c>
@@ -15481,19 +15539,19 @@
       <c r="U62" s="2">
         <v>158</v>
       </c>
-      <c r="V62" s="66">
+      <c r="V62" s="65">
         <f>SUM(R62:U62)</f>
         <v>603</v>
       </c>
       <c r="W62" s="2">
         <v>157</v>
       </c>
-      <c r="AA62" s="66">
+      <c r="AA62" s="65">
         <f>SUM(W62:Z62)</f>
         <v>157</v>
       </c>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B63" s="19" t="s">
         <v>36</v>
       </c>
@@ -15509,11 +15567,11 @@
       <c r="F63" s="19">
         <v>0.71699999999999997</v>
       </c>
-      <c r="G63" s="67">
+      <c r="G63" s="66">
         <f>G62/G58</f>
         <v>0.69974554707379133</v>
       </c>
-      <c r="H63" s="26">
+      <c r="H63" s="25">
         <v>0.70399999999999996</v>
       </c>
       <c r="I63" s="19">
@@ -15525,7 +15583,7 @@
       <c r="K63" s="19">
         <v>0.70299999999999996</v>
       </c>
-      <c r="L63" s="67">
+      <c r="L63" s="66">
         <f>L62/L58</f>
         <v>0.68866328257191201</v>
       </c>
@@ -15541,7 +15599,7 @@
       <c r="P63" s="19">
         <v>0.70599999999999996</v>
       </c>
-      <c r="Q63" s="67">
+      <c r="Q63" s="66">
         <f>Q62/Q58</f>
         <v>0.6845070422535211</v>
       </c>
@@ -15557,7 +15615,7 @@
       <c r="U63" s="19">
         <v>0.71799999999999997</v>
       </c>
-      <c r="V63" s="67">
+      <c r="V63" s="66">
         <f>V62/V58</f>
         <v>0.71024734982332161</v>
       </c>
@@ -15567,12 +15625,12 @@
       <c r="X63" s="19"/>
       <c r="Y63" s="19"/>
       <c r="Z63" s="19"/>
-      <c r="AA63" s="67" t="e">
+      <c r="AA63" s="66" t="e">
         <f>AA62/AA58</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
         <v>54</v>
       </c>
@@ -15588,7 +15646,7 @@
       <c r="F64" s="2">
         <v>5</v>
       </c>
-      <c r="G64" s="66">
+      <c r="G64" s="65">
         <f>SUM(C64:F64)</f>
         <v>35</v>
       </c>
@@ -15604,7 +15662,7 @@
       <c r="K64" s="2">
         <v>14</v>
       </c>
-      <c r="L64" s="66">
+      <c r="L64" s="65">
         <f>SUM(H64:K64)</f>
         <v>74</v>
       </c>
@@ -15620,7 +15678,7 @@
       <c r="P64" s="2">
         <v>14</v>
       </c>
-      <c r="Q64" s="66">
+      <c r="Q64" s="65">
         <f>SUM(M64:P64)</f>
         <v>76</v>
       </c>
@@ -15636,14 +15694,14 @@
       <c r="U64" s="2">
         <v>24</v>
       </c>
-      <c r="V64" s="66">
+      <c r="V64" s="65">
         <f>SUM(R64:U64)</f>
         <v>119</v>
       </c>
       <c r="W64" s="2">
         <v>23</v>
       </c>
-      <c r="AA64" s="66">
+      <c r="AA64" s="65">
         <f>SUM(W64:Z64)</f>
         <v>23</v>
       </c>
@@ -15664,7 +15722,7 @@
       <c r="F65" s="19">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="G65" s="67">
+      <c r="G65" s="66">
         <f>G64/G58</f>
         <v>8.9058524173027995E-2</v>
       </c>
@@ -15680,7 +15738,7 @@
       <c r="K65" s="19">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="L65" s="67">
+      <c r="L65" s="66">
         <f>L64/L58</f>
         <v>0.12521150592216582</v>
       </c>
@@ -15696,7 +15754,7 @@
       <c r="P65" s="19">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="Q65" s="67">
+      <c r="Q65" s="66">
         <f>Q64/Q58</f>
         <v>0.10704225352112676</v>
       </c>
@@ -15712,7 +15770,7 @@
       <c r="U65" s="19">
         <v>0.107</v>
       </c>
-      <c r="V65" s="67">
+      <c r="V65" s="66">
         <f>V64/V58</f>
         <v>0.14016489988221437</v>
       </c>
@@ -15722,7 +15780,7 @@
       <c r="X65" s="19"/>
       <c r="Y65" s="19"/>
       <c r="Z65" s="19"/>
-      <c r="AA65" s="67" t="e">
+      <c r="AA65" s="66" t="e">
         <f>AA64/AA58</f>
         <v>#DIV/0!</v>
       </c>
@@ -15731,11 +15789,11 @@
       <c r="B66" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G66" s="66">
+      <c r="G66" s="65">
         <f>SUM(C66:F66)</f>
         <v>0</v>
       </c>
-      <c r="L66" s="66">
+      <c r="L66" s="65">
         <f>SUM(H66:K66)</f>
         <v>0</v>
       </c>
@@ -15751,7 +15809,7 @@
       <c r="P66" s="2">
         <v>-18</v>
       </c>
-      <c r="Q66" s="66">
+      <c r="Q66" s="65">
         <f>SUM(M66:P66)</f>
         <v>-46</v>
       </c>
@@ -15767,14 +15825,14 @@
       <c r="U66" s="2">
         <v>-9</v>
       </c>
-      <c r="V66" s="66">
+      <c r="V66" s="65">
         <f>SUM(R66:U66)</f>
         <v>-9</v>
       </c>
       <c r="W66" s="2">
         <v>-7</v>
       </c>
-      <c r="AA66" s="66">
+      <c r="AA66" s="65">
         <f>SUM(W66:Z66)</f>
         <v>-7</v>
       </c>
@@ -15787,15 +15845,15 @@
       <c r="D67" s="19"/>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
-      <c r="G67" s="67">
+      <c r="G67" s="66">
         <f>G66/G58</f>
         <v>0</v>
       </c>
-      <c r="H67" s="26"/>
+      <c r="H67" s="25"/>
       <c r="I67" s="19"/>
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
-      <c r="L67" s="67">
+      <c r="L67" s="66">
         <f>L66/L58</f>
         <v>0</v>
       </c>
@@ -15813,7 +15871,7 @@
       <c r="P67" s="19">
         <v>-9.9000000000000005E-2</v>
       </c>
-      <c r="Q67" s="67">
+      <c r="Q67" s="66">
         <f>Q66/Q58</f>
         <v>-6.4788732394366194E-2</v>
       </c>
@@ -15830,7 +15888,7 @@
       <c r="U67" s="19">
         <v>-4.2000000000000003E-2</v>
       </c>
-      <c r="V67" s="67">
+      <c r="V67" s="66">
         <f>V66/V58</f>
         <v>-1.0600706713780919E-2</v>
       </c>
@@ -15840,74 +15898,74 @@
       <c r="X67" s="19"/>
       <c r="Y67" s="19"/>
       <c r="Z67" s="19"/>
-      <c r="AA67" s="67" t="e">
+      <c r="AA67" s="66" t="e">
         <f>AA66/AA58</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="68" spans="2:27" ht="20" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="44" t="s">
+      <c r="B68" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C68" s="45">
+      <c r="C68" s="44">
         <v>43</v>
       </c>
-      <c r="D68" s="45">
+      <c r="D68" s="44">
         <v>45</v>
       </c>
-      <c r="E68" s="45">
+      <c r="E68" s="44">
         <v>45</v>
       </c>
-      <c r="F68" s="45">
+      <c r="F68" s="44">
         <v>50</v>
       </c>
-      <c r="G68" s="53"/>
-      <c r="H68" s="46">
+      <c r="G68" s="52"/>
+      <c r="H68" s="45">
         <v>51</v>
       </c>
-      <c r="I68" s="45">
+      <c r="I68" s="44">
         <v>52</v>
       </c>
-      <c r="J68" s="45">
+      <c r="J68" s="44">
         <v>54</v>
       </c>
-      <c r="K68" s="45">
+      <c r="K68" s="44">
         <v>55</v>
       </c>
-      <c r="L68" s="53"/>
-      <c r="M68" s="45">
+      <c r="L68" s="52"/>
+      <c r="M68" s="44">
         <v>59</v>
       </c>
-      <c r="N68" s="45">
+      <c r="N68" s="44">
         <v>62</v>
       </c>
-      <c r="O68" s="45">
+      <c r="O68" s="44">
         <v>64</v>
       </c>
-      <c r="P68" s="45">
+      <c r="P68" s="44">
         <v>67</v>
       </c>
-      <c r="Q68" s="53"/>
-      <c r="R68" s="45">
+      <c r="Q68" s="52"/>
+      <c r="R68" s="44">
         <v>68</v>
       </c>
-      <c r="S68" s="45">
+      <c r="S68" s="44">
         <v>72</v>
       </c>
-      <c r="T68" s="45">
+      <c r="T68" s="44">
         <v>72</v>
       </c>
-      <c r="U68" s="44">
+      <c r="U68" s="43">
         <v>73</v>
       </c>
-      <c r="V68" s="50"/>
-      <c r="W68" s="44">
+      <c r="V68" s="49"/>
+      <c r="W68" s="43">
         <v>75</v>
       </c>
-      <c r="X68" s="44"/>
-      <c r="Y68" s="44"/>
-      <c r="Z68" s="44"/>
-      <c r="AA68" s="50"/>
+      <c r="X68" s="43"/>
+      <c r="Y68" s="43"/>
+      <c r="Z68" s="43"/>
+      <c r="AA68" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15939,9 +15997,9 @@
       <c r="A2" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="83">
+      <c r="D2" s="78">
         <f>SUM(D5:D8)</f>
-        <v>945</v>
+        <v>930</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15950,9 +16008,9 @@
       <c r="M2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="83">
+      <c r="A3" s="78">
         <f>Modell!AG13</f>
-        <v>943.75999999999976</v>
+        <v>923.75999999999976</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
@@ -15961,19 +16019,19 @@
       <c r="M3"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="53" t="s">
         <v>146</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="53" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="53" t="s">
         <v>142</v>
       </c>
       <c r="I4"/>
@@ -15983,20 +16041,20 @@
       <c r="M4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C5" s="54" t="s">
+      <c r="C5" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="56">
+      <c r="D5" s="55">
         <v>700</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="53">
         <v>15</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="55">
         <f>D5*E5</f>
         <v>10500</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="56">
         <f>F5/Modell!$B$5</f>
         <v>73.520072450180351</v>
       </c>
@@ -16007,20 +16065,20 @@
       <c r="M5"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="D6" s="56">
+      <c r="D6" s="55">
         <v>90</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="53">
         <v>6</v>
       </c>
-      <c r="F6" s="56">
+      <c r="F6" s="55">
         <f>D6*E6</f>
         <v>540</v>
       </c>
-      <c r="G6" s="57">
+      <c r="G6" s="56">
         <f>F6/Modell!$B$5</f>
         <v>3.7810322974378465</v>
       </c>
@@ -16031,22 +16089,22 @@
       <c r="M6"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C7" s="54" t="s">
+      <c r="C7" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="56">
-        <v>135</v>
-      </c>
-      <c r="E7" s="54">
+      <c r="D7" s="55">
+        <v>120</v>
+      </c>
+      <c r="E7" s="53">
         <v>7</v>
       </c>
-      <c r="F7" s="56">
+      <c r="F7" s="55">
         <f t="shared" ref="F7:F8" si="0">D7*E7</f>
-        <v>945</v>
-      </c>
-      <c r="G7" s="57">
+        <v>840</v>
+      </c>
+      <c r="G7" s="56">
         <f>F7/Modell!$B$5</f>
-        <v>6.6168065205162314</v>
+        <v>5.8816057960144281</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -16055,20 +16113,20 @@
       <c r="M7"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="56">
+      <c r="D8" s="55">
         <v>20</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="53">
         <v>5</v>
       </c>
-      <c r="F8" s="56">
+      <c r="F8" s="55">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="G8" s="57">
+      <c r="G8" s="56">
         <f>F8/Modell!$B$5</f>
         <v>0.70019116619219379</v>
       </c>
@@ -16079,18 +16137,18 @@
       <c r="M8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="58">
+      <c r="D9" s="57"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="57">
         <f>SUM(F5:F8)</f>
-        <v>12085</v>
-      </c>
-      <c r="G9" s="59">
+        <v>11980</v>
+      </c>
+      <c r="G9" s="58">
         <f>SUM(G5:G8)</f>
-        <v>84.61810243432663</v>
+        <v>83.882901709824822</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -16099,11 +16157,11 @@
       <c r="M9"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="61"/>
-      <c r="G10" s="62"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="61"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -16111,16 +16169,16 @@
       <c r="M10"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="56">
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="55">
         <f>Modell!B7</f>
         <v>736</v>
       </c>
-      <c r="G11" s="57">
+      <c r="G11" s="56">
         <f>F11/Modell!$B$5</f>
         <v>5.1534069831745466</v>
       </c>
@@ -16131,16 +16189,16 @@
       <c r="M11"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="56">
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="55">
         <f>Modell!B8</f>
         <v>2728</v>
       </c>
-      <c r="G12" s="57">
+      <c r="G12" s="56">
         <f>-F12/Modell!$B$5</f>
         <v>-19.101215013723046</v>
       </c>
@@ -16151,11 +16209,11 @@
       <c r="M12"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C13" s="63"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="64"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="63"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -16163,18 +16221,18 @@
       <c r="M13"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="58">
+      <c r="D14" s="54"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="57">
         <f>F9+F11-F12</f>
-        <v>10093</v>
-      </c>
-      <c r="G14" s="59">
+        <v>9988</v>
+      </c>
+      <c r="G14" s="58">
         <f>SUM(G9:G12)</f>
-        <v>70.670294403778129</v>
+        <v>69.935093679276321</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -16183,11 +16241,11 @@
       <c r="M14"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="25"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -16228,51 +16286,51 @@
       <c r="C5" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="40">
         <f>Modell!$B$9/Modell!AG9</f>
-        <v>5.215041894259949</v>
-      </c>
-      <c r="E5" s="41">
+        <v>5.2608228084797206</v>
+      </c>
+      <c r="E5" s="40">
         <f>Modell!$B$9/Modell!AH9</f>
-        <v>4.8716204493627924</v>
-      </c>
-      <c r="F5" s="41">
+        <v>4.9143865943767082</v>
+      </c>
+      <c r="F5" s="40">
         <f>Modell!$B$9/Modell!AI9</f>
-        <v>4.5514598401491932</v>
+        <v>4.5914154141870451</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <f>Modell!$B$9/Modell!AG13</f>
-        <v>10.342996965330171</v>
-      </c>
-      <c r="E6" s="41">
+        <v>10.659692669091541</v>
+      </c>
+      <c r="E6" s="40">
         <f>Modell!$B$9/Modell!AH13</f>
-        <v>9.5456850635113835</v>
-      </c>
-      <c r="F6" s="41">
+        <v>9.8333450836858152</v>
+      </c>
+      <c r="F6" s="40">
         <f>Modell!$B$9/Modell!AI13</f>
-        <v>8.4607033208316622</v>
+        <v>8.6963731120557668</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="62" x14ac:dyDescent="0.7">
       <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="40">
         <f>Modell!$B$4/Modell!AG20</f>
-        <v>14.487707996158006</v>
-      </c>
-      <c r="E7" s="41">
+        <v>15.100757306752078</v>
+      </c>
+      <c r="E7" s="40">
         <f>Modell!$B$4/Modell!AH20</f>
-        <v>13.052264484729314</v>
-      </c>
-      <c r="F7" s="41">
+        <v>13.585644344039178</v>
+      </c>
+      <c r="F7" s="40">
         <f>Modell!$B$4/Modell!AI20</f>
-        <v>11.159099042549036</v>
+        <v>11.568517012948545</v>
       </c>
     </row>
   </sheetData>
@@ -16372,7 +16430,7 @@
       <c r="I4" s="16">
         <v>7200</v>
       </c>
-      <c r="J4" s="79">
+      <c r="J4" s="16">
         <f>I4*1.06</f>
         <v>7632</v>
       </c>
@@ -16414,7 +16472,7 @@
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="38">
+      <c r="A5" s="37">
         <f>V25</f>
         <v>33.079713172610681</v>
       </c>
@@ -16439,7 +16497,7 @@
       <c r="I5" s="15">
         <v>-1821</v>
       </c>
-      <c r="J5" s="80">
+      <c r="J5" s="15">
         <f>J4*-0.24</f>
         <v>-1831.6799999999998</v>
       </c>
@@ -16483,7 +16541,7 @@
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <f>V26</f>
-        <v>-0.391917037268186</v>
+        <v>-0.39855066958889668</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>51</v>
@@ -16512,12 +16570,12 @@
         <f>SUM(I4:I5)</f>
         <v>5379</v>
       </c>
-      <c r="J6" s="80">
+      <c r="J6" s="15">
         <f t="shared" ref="J6" si="3">SUM(J4:J5)</f>
         <v>5800.32</v>
       </c>
       <c r="K6" s="15">
-        <f t="shared" ref="J6:S6" si="4">SUM(K4:K5)</f>
+        <f t="shared" ref="K6:S6" si="4">SUM(K4:K5)</f>
         <v>5647.68</v>
       </c>
       <c r="L6" s="15">
@@ -16575,7 +16633,7 @@
       <c r="I7" s="15">
         <v>-805</v>
       </c>
-      <c r="J7" s="80">
+      <c r="J7" s="15">
         <f>I7*1.08</f>
         <v>-869.40000000000009</v>
       </c>
@@ -16638,7 +16696,7 @@
       <c r="I8" s="15">
         <v>-2886</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="15">
         <f>I8*1.08</f>
         <v>-3116.88</v>
       </c>
@@ -16707,12 +16765,12 @@
         <f>SUM(I6:I8)</f>
         <v>1688</v>
       </c>
-      <c r="J9" s="79">
+      <c r="J9" s="16">
         <f t="shared" ref="J9" si="9">SUM(J6:J8)</f>
         <v>1814.04</v>
       </c>
       <c r="K9" s="16">
-        <f t="shared" ref="J9:S9" si="10">SUM(K6:K8)</f>
+        <f t="shared" ref="K9:S9" si="10">SUM(K6:K8)</f>
         <v>1661.4000000000005</v>
       </c>
       <c r="L9" s="16">
@@ -16770,7 +16828,7 @@
       <c r="I10" s="15">
         <v>-702</v>
       </c>
-      <c r="J10" s="80">
+      <c r="J10" s="15">
         <v>-728</v>
       </c>
       <c r="K10" s="15">
@@ -16782,7 +16840,7 @@
         <v>-728</v>
       </c>
       <c r="M10" s="15">
-        <f t="shared" ref="L10:S10" si="11">L10*1.01</f>
+        <f t="shared" ref="M10:S10" si="11">L10*1.01</f>
         <v>-735.28</v>
       </c>
       <c r="N10" s="15">
@@ -16838,12 +16896,12 @@
         <f>SUM(I9:I10)</f>
         <v>986</v>
       </c>
-      <c r="J11" s="79">
+      <c r="J11" s="16">
         <f t="shared" ref="J11" si="13">SUM(J9:J10)</f>
         <v>1086.04</v>
       </c>
       <c r="K11" s="16">
-        <f t="shared" ref="J11:S11" si="14">SUM(K9:K10)</f>
+        <f t="shared" ref="K11:S11" si="14">SUM(K9:K10)</f>
         <v>933.40000000000055</v>
       </c>
       <c r="L11" s="16">
@@ -16901,7 +16959,7 @@
       <c r="I12" s="15">
         <v>-124</v>
       </c>
-      <c r="J12" s="80">
+      <c r="J12" s="15">
         <v>-130</v>
       </c>
       <c r="K12" s="15">
@@ -16913,7 +16971,7 @@
         <v>-130</v>
       </c>
       <c r="M12" s="15">
-        <f t="shared" ref="L12:S12" si="15">L12*1.01</f>
+        <f t="shared" ref="M12:S12" si="15">L12*1.01</f>
         <v>-131.30000000000001</v>
       </c>
       <c r="N12" s="15">
@@ -16969,12 +17027,12 @@
         <f>SUM(I11:I12)</f>
         <v>862</v>
       </c>
-      <c r="J13" s="79">
+      <c r="J13" s="16">
         <f t="shared" ref="J13" si="17">SUM(J11:J12)</f>
         <v>956.04</v>
       </c>
       <c r="K13" s="16">
-        <f t="shared" ref="J13:S13" si="18">SUM(K11:K12)</f>
+        <f t="shared" ref="K13:S13" si="18">SUM(K11:K12)</f>
         <v>803.40000000000055</v>
       </c>
       <c r="L13" s="16">
@@ -17032,7 +17090,7 @@
       <c r="I14" s="15">
         <v>321</v>
       </c>
-      <c r="J14" s="80">
+      <c r="J14" s="15">
         <f>I14*1.02</f>
         <v>327.42</v>
       </c>
@@ -17095,7 +17153,7 @@
       <c r="I15" s="15">
         <v>-593</v>
       </c>
-      <c r="J15" s="80">
+      <c r="J15" s="15">
         <f>I15*1.02</f>
         <v>-604.86</v>
       </c>
@@ -17164,12 +17222,12 @@
         <f>SUM(I13:I15)</f>
         <v>590</v>
       </c>
-      <c r="J16" s="80">
+      <c r="J16" s="15">
         <f t="shared" ref="J16" si="21">SUM(J13:J15)</f>
         <v>678.6</v>
       </c>
       <c r="K16" s="15">
-        <f t="shared" ref="J16:S16" si="22">SUM(K13:K15)</f>
+        <f t="shared" ref="K16:S16" si="22">SUM(K13:K15)</f>
         <v>520.41120000000046</v>
       </c>
       <c r="L16" s="15">
@@ -17227,7 +17285,7 @@
       <c r="I17" s="15">
         <v>-136</v>
       </c>
-      <c r="J17" s="80">
+      <c r="J17" s="15">
         <f>J16*-0.2</f>
         <v>-135.72</v>
       </c>
@@ -17296,12 +17354,12 @@
         <f>SUM(I16:I17)</f>
         <v>454</v>
       </c>
-      <c r="J18" s="79">
+      <c r="J18" s="16">
         <f t="shared" ref="J18" si="25">SUM(J16:J17)</f>
         <v>542.88</v>
       </c>
       <c r="K18" s="16">
-        <f t="shared" ref="J18:S18" si="26">SUM(K16:K17)</f>
+        <f t="shared" ref="K18:S18" si="26">SUM(K16:K17)</f>
         <v>416.32896000000039</v>
       </c>
       <c r="L18" s="16">
@@ -18066,55 +18124,55 @@
       </c>
     </row>
     <row r="19" spans="3:201" x14ac:dyDescent="0.25">
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>37.181941999999999</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>150</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>149.05500000000001</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="29">
         <v>147.423677</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="29">
         <v>146.64874800000001</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="J19" s="81">
+      <c r="J19" s="29">
         <v>141.96249399999999</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="O19" s="30">
+      <c r="O19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="P19" s="30">
+      <c r="P19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="Q19" s="30">
+      <c r="Q19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="R19" s="30">
+      <c r="R19" s="29">
         <v>142.81814</v>
       </c>
-      <c r="S19" s="30">
+      <c r="S19" s="29">
         <v>142.81814</v>
       </c>
     </row>
@@ -18122,67 +18180,67 @@
       <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="30">
         <f t="shared" ref="D20:H20" si="30">D18/D19</f>
         <v>-5.2444813129986594</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <f t="shared" si="30"/>
         <v>0.34</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <f t="shared" si="30"/>
         <v>2.2005300057025927</v>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="30">
         <f t="shared" si="30"/>
         <v>2.1095661587656642</v>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="30">
         <f t="shared" si="30"/>
         <v>2.4957594591942915</v>
       </c>
-      <c r="I20" s="31">
+      <c r="I20" s="30">
         <f>I18/I19</f>
         <v>3.1788678945125599</v>
       </c>
-      <c r="J20" s="82">
+      <c r="J20" s="30">
         <f t="shared" ref="J20" si="31">J18/J19</f>
         <v>3.8241086409766796</v>
       </c>
-      <c r="K20" s="31">
-        <f t="shared" ref="J20:S20" si="32">K18/K19</f>
+      <c r="K20" s="30">
+        <f t="shared" ref="K20:S20" si="32">K18/K19</f>
         <v>2.9150986002198347</v>
       </c>
-      <c r="L20" s="31">
+      <c r="L20" s="30">
         <f t="shared" si="32"/>
         <v>2.8833951989572224</v>
       </c>
-      <c r="M20" s="31">
+      <c r="M20" s="30">
         <f t="shared" si="32"/>
         <v>2.851696304012922</v>
       </c>
-      <c r="N20" s="31">
+      <c r="N20" s="30">
         <f t="shared" si="32"/>
         <v>2.8183830515064847</v>
       </c>
-      <c r="O20" s="31">
+      <c r="O20" s="30">
         <f t="shared" si="32"/>
         <v>2.7834425703076215</v>
       </c>
-      <c r="P20" s="31">
+      <c r="P20" s="30">
         <f t="shared" si="32"/>
         <v>2.7468616338254828</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="30">
         <f t="shared" si="32"/>
         <v>2.7086266548410389</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="30">
         <f t="shared" si="32"/>
         <v>2.6687236802263028</v>
       </c>
-      <c r="S20" s="31">
+      <c r="S20" s="30">
         <f t="shared" si="32"/>
         <v>2.6271383855483563</v>
       </c>
@@ -18193,7 +18251,7 @@
       <c r="U21" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="V21" s="36">
+      <c r="V21" s="35">
         <v>0.08</v>
       </c>
     </row>
@@ -18265,7 +18323,7 @@
       <c r="U22" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="V22" s="36">
+      <c r="V22" s="35">
         <v>-0.01</v>
       </c>
     </row>
@@ -18301,10 +18359,10 @@
       <c r="Q23" s="13"/>
       <c r="R23" s="13"/>
       <c r="S23" s="13"/>
-      <c r="U23" s="35" t="s">
+      <c r="U23" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="V23" s="37">
+      <c r="V23" s="36">
         <f>NPV(V21,J18:GS18)</f>
         <v>4724.3831070457563</v>
       </c>
@@ -18357,7 +18415,7 @@
       <c r="U25" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="V25" s="38">
+      <c r="V25" s="37">
         <f>V23/V24</f>
         <v>33.079713172610681</v>
       </c>
@@ -18435,7 +18493,7 @@
       </c>
       <c r="V26" s="14">
         <f>(V25-Modell!B4)/Modell!B4</f>
-        <v>-0.391917037268186</v>
+        <v>-0.39855066958889668</v>
       </c>
     </row>
     <row r="27" spans="3:201" x14ac:dyDescent="0.25">
